--- a/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -15,7 +15,7 @@
     <sheet sheetId="9" name="Financial Health" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$F40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="208">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -222,36 +222,36 @@
     <t>WEIGHTED ENROLLMENT POPULATIONS</t>
   </si>
   <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>Year 5</t>
+  </si>
+  <si>
     <t>Special Education (SPED)</t>
   </si>
   <si>
-    <t>3  /  4  /  5  /  6  /  6</t>
-  </si>
-  <si>
     <t>English Language Learners (ELL)</t>
   </si>
   <si>
-    <t>2  /  3  /  4  /  5  /  5</t>
-  </si>
-  <si>
     <t>Economically Disadvantaged</t>
   </si>
   <si>
-    <t>5  /  7  /  9  /  10  /  12</t>
-  </si>
-  <si>
     <t>Total Weighted Students</t>
   </si>
   <si>
-    <t>10  /  14  /  18  /  21  /  23</t>
-  </si>
-  <si>
     <t>Weighted % of Enrollment</t>
   </si>
   <si>
-    <t>67%  /  64%  /  60%  /  58%  /  57%</t>
-  </si>
-  <si>
     <t>GROWTH &amp; ESCALATION ASSUMPTIONS</t>
   </si>
   <si>
@@ -268,21 +268,6 @@
   </si>
   <si>
     <t>5 Years</t>
-  </si>
-  <si>
-    <t>Year 1</t>
-  </si>
-  <si>
-    <t>Year 2</t>
-  </si>
-  <si>
-    <t>Year 3</t>
-  </si>
-  <si>
-    <t>Year 4</t>
-  </si>
-  <si>
-    <t>Year 5</t>
   </si>
   <si>
     <t>Students</t>
@@ -930,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -956,8 +941,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1523,11 +1514,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1730,87 +1722,181 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>60</v>
       </c>
       <c r="B28" s="8"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="C29" s="25" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D29" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="B30" s="26">
+        <v>3</v>
+      </c>
+      <c r="C30" s="26">
+        <v>4</v>
+      </c>
+      <c r="D30" s="26">
+        <v>5</v>
+      </c>
+      <c r="E30" s="26">
+        <v>6</v>
+      </c>
+      <c r="F30" s="26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B31" s="26">
+        <v>2</v>
+      </c>
+      <c r="C31" s="26">
+        <v>3</v>
+      </c>
+      <c r="D31" s="26">
+        <v>4</v>
+      </c>
+      <c r="E31" s="26">
+        <v>5</v>
+      </c>
+      <c r="F31" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="26" t="s">
+      <c r="B32" s="26">
+        <v>5</v>
+      </c>
+      <c r="C32" s="26">
+        <v>7</v>
+      </c>
+      <c r="D32" s="26">
+        <v>9</v>
+      </c>
+      <c r="E32" s="26">
+        <v>10</v>
+      </c>
+      <c r="F32" s="26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="28">
+        <f>B30+B31+B32</f>
+        <v>10</v>
+      </c>
+      <c r="C33" s="28">
+        <f>C30+C31+C32</f>
+        <v>14</v>
+      </c>
+      <c r="D33" s="28">
+        <f>D30+D31+D32</f>
+        <v>18</v>
+      </c>
+      <c r="E33" s="28">
+        <f>E30+E31+E32</f>
+        <v>21</v>
+      </c>
+      <c r="F33" s="28">
+        <f>F30+F31+F32</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="29" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="B34" s="30">
+        <f>IF(B22=0,0,B33/B22)</f>
+        <v>0.66666667</v>
+      </c>
+      <c r="C34" s="30">
+        <f>IF(C23=0,0,C33/C23)</f>
+        <v>0.63636364</v>
+      </c>
+      <c r="D34" s="30">
+        <f>IF(D24=0,0,D33/D24)</f>
+        <v>0.6</v>
+      </c>
+      <c r="E34" s="30">
+        <f>IF(E25=0,0,E33/E25)</f>
+        <v>0.58333333</v>
+      </c>
+      <c r="F34" s="30">
+        <f>IF(F26=0,0,F33/F26)</f>
+        <v>0.575</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="8"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" s="27">
-        <v>0.03</v>
-      </c>
+      <c r="B36" s="8"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="27">
-        <v>0.025</v>
+        <v>72</v>
+      </c>
+      <c r="B37" s="31">
+        <v>0.03</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="28">
-        <v>0.8333333333333334</v>
+        <v>73</v>
+      </c>
+      <c r="B38" s="31">
+        <v>0.025</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" s="32">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="29" t="s">
+      <c r="B40" s="33" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1840,53 +1926,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>81</v>
+      <c r="B1" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="31">
+        <v>77</v>
+      </c>
+      <c r="B2" s="35">
         <f>Assumptions!B22</f>
         <v>15</v>
       </c>
-      <c r="C2" s="31">
+      <c r="C2" s="35">
         <f>Assumptions!B23</f>
         <v>22</v>
       </c>
-      <c r="D2" s="31">
+      <c r="D2" s="35">
         <f>Assumptions!B24</f>
         <v>30</v>
       </c>
-      <c r="E2" s="31">
+      <c r="E2" s="35">
         <f>Assumptions!B25</f>
         <v>36</v>
       </c>
-      <c r="F2" s="31">
+      <c r="F2" s="35">
         <f>Assumptions!B26</f>
         <v>40</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1896,82 +1982,82 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" s="32">
+        <v>79</v>
+      </c>
+      <c r="B4" s="36">
         <f>6000*Assumptions!B22</f>
         <v>90000</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="36">
         <f>6180*Assumptions!B23</f>
         <v>135960</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="36">
         <f>6365*Assumptions!B24</f>
         <v>190950</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="36">
         <f>6556*Assumptions!B25</f>
         <v>236016</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="36">
         <f>6753*Assumptions!B26</f>
         <v>270120</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="32">
+        <v>80</v>
+      </c>
+      <c r="B5" s="36">
         <f>200*Assumptions!B22</f>
         <v>3000</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="36">
         <f>200*Assumptions!B23</f>
         <v>4400</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="36">
         <f>200*Assumptions!B24</f>
         <v>6000</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="36">
         <f>200*Assumptions!B25</f>
         <v>7200</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="36">
         <f>200*Assumptions!B26</f>
         <v>8000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="33">
+        <v>81</v>
+      </c>
+      <c r="B6" s="37">
         <f>SUM(B4:B5)</f>
         <v>93000</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="37">
         <f>SUM(C4:C5)</f>
         <v>140360</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="37">
         <f>SUM(D4:D5)</f>
         <v>196950</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="37">
         <f>SUM(E4:E5)</f>
         <v>243216</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="37">
         <f>SUM(F4:F5)</f>
         <v>278120</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1981,57 +2067,57 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="32">
+        <v>83</v>
+      </c>
+      <c r="B8" s="36">
         <f>7000*Assumptions!B22</f>
         <v>105000</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="36">
         <f>7210*Assumptions!B23</f>
         <v>158620</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="36">
         <f>7426*Assumptions!B24</f>
         <v>222780</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="36">
         <f>7649*Assumptions!B25</f>
         <v>275364</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="36">
         <f>7878*Assumptions!B26</f>
         <v>315120</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="33">
+        <v>84</v>
+      </c>
+      <c r="B9" s="37">
         <f>SUM(B8:B8)</f>
         <v>105000</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="37">
         <f>SUM(C8:C8)</f>
         <v>158620</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="37">
         <f>SUM(D8:D8)</f>
         <v>222780</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="37">
         <f>SUM(E8:E8)</f>
         <v>275364</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="37">
         <f>SUM(F8:F8)</f>
         <v>315120</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2041,70 +2127,70 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="32">
+        <v>86</v>
+      </c>
+      <c r="B11" s="36">
         <v>3000</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="36">
         <v>4000</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="36">
         <v>5000</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="36">
         <v>5000</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="36">
         <v>5000</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="33">
+        <v>87</v>
+      </c>
+      <c r="B12" s="37">
         <f>SUM(B11:B11)</f>
         <v>3000</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="37">
         <f>SUM(C11:C11)</f>
         <v>4000</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="37">
         <f>SUM(D11:D11)</f>
         <v>5000</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="37">
         <f>SUM(E11:E11)</f>
         <v>5000</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="37">
         <f>SUM(F11:F11)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="33">
+        <v>88</v>
+      </c>
+      <c r="B14" s="37">
         <f>B6+B9+B12</f>
         <v>201000</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="37">
         <f>C6+C9+C12</f>
         <v>302980</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="37">
         <f>D6+D9+D12</f>
         <v>424730</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="37">
         <f>E6+E9+E12</f>
         <v>523580</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="37">
         <f>F6+F9+F12</f>
         <v>598240</v>
       </c>
@@ -2133,7 +2219,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -2144,86 +2230,86 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="G3" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="H3" s="34" t="s">
         <v>97</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" s="30" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="28">
+        <v>100</v>
+      </c>
+      <c r="D4" s="32">
         <v>1</v>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="38">
         <v>48000</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="31">
         <v>0.2</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="39">
         <v>61272</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="28">
+        <v>103</v>
+      </c>
+      <c r="D5" s="32">
         <v>0.5</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="38">
         <v>30000</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="31">
         <v>0</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="39">
         <v>16147.5</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2235,63 +2321,63 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="25">
+        <v>105</v>
+      </c>
+      <c r="B8" s="27">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="25">
+        <v>106</v>
+      </c>
+      <c r="B9" s="27">
         <v>1.5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="36">
+        <v>107</v>
+      </c>
+      <c r="B10" s="40">
         <v>63000</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="B11" s="36">
+        <v>108</v>
+      </c>
+      <c r="B11" s="40">
         <v>9600</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" s="36">
+        <v>109</v>
+      </c>
+      <c r="B12" s="40">
         <v>4820</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="36">
+        <v>110</v>
+      </c>
+      <c r="B13" s="40">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="37">
+      <c r="A14" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="41">
         <v>77420</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -2300,112 +2386,112 @@
       <c r="F16" s="8"/>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>81</v>
+      <c r="B17" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" s="32">
+        <v>113</v>
+      </c>
+      <c r="B18" s="36">
         <v>77420</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="36">
         <v>77420</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="36">
         <v>77420</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="36">
         <v>77420</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="36">
         <v>77420</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="38">
-        <f>(1+Assumptions!B36)^0</f>
+        <v>114</v>
+      </c>
+      <c r="B19" s="42">
+        <f>(1+Assumptions!B37)^0</f>
         <v>1</v>
       </c>
-      <c r="C19" s="38">
-        <f>(1+Assumptions!B36)^1</f>
+      <c r="C19" s="42">
+        <f>(1+Assumptions!B37)^1</f>
         <v>1.03</v>
       </c>
-      <c r="D19" s="38">
-        <f>(1+Assumptions!B36)^2</f>
+      <c r="D19" s="42">
+        <f>(1+Assumptions!B37)^2</f>
         <v>1.0609</v>
       </c>
-      <c r="E19" s="38">
-        <f>(1+Assumptions!B36)^3</f>
+      <c r="E19" s="42">
+        <f>(1+Assumptions!B37)^3</f>
         <v>1.092727</v>
       </c>
-      <c r="F19" s="38">
-        <f>(1+Assumptions!B36)^4</f>
+      <c r="F19" s="42">
+        <f>(1+Assumptions!B37)^4</f>
         <v>1.1255088100000001</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="B20" s="39">
-        <f>Assumptions!B38</f>
+        <v>115</v>
+      </c>
+      <c r="B20" s="43">
+        <f>Assumptions!B39</f>
         <v>0.8333333333333334</v>
       </c>
-      <c r="C20" s="39">
+      <c r="C20" s="43">
         <v>1</v>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="43">
         <v>1</v>
       </c>
-      <c r="E20" s="39">
+      <c r="E20" s="43">
         <v>1</v>
       </c>
-      <c r="F20" s="39">
+      <c r="F20" s="43">
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B21" s="33">
+        <v>116</v>
+      </c>
+      <c r="B21" s="37">
         <f>B18*B19*B20</f>
         <v>64516</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="37">
         <f>C18*C19*C20</f>
         <v>79742</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="37">
         <f>D18*D19*D20</f>
         <v>82134</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="37">
         <f>E18*E19*E20</f>
         <v>84598</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="37">
         <f>F18*F19*F20</f>
         <v>87136</v>
       </c>
@@ -2436,53 +2522,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>81</v>
+      <c r="B1" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="31">
+        <v>77</v>
+      </c>
+      <c r="B2" s="35">
         <f>Assumptions!B22</f>
         <v>15</v>
       </c>
-      <c r="C2" s="31">
+      <c r="C2" s="35">
         <f>Assumptions!B23</f>
         <v>22</v>
       </c>
-      <c r="D2" s="31">
+      <c r="D2" s="35">
         <f>Assumptions!B24</f>
         <v>30</v>
       </c>
-      <c r="E2" s="31">
+      <c r="E2" s="35">
         <f>Assumptions!B25</f>
         <v>36</v>
       </c>
-      <c r="F2" s="31">
+      <c r="F2" s="35">
         <f>Assumptions!B26</f>
         <v>40</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2492,57 +2578,57 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" s="32">
+        <v>118</v>
+      </c>
+      <c r="B4" s="36">
         <f>400*Assumptions!B22</f>
         <v>6000</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="36">
         <f>412*Assumptions!B23</f>
         <v>9064</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="36">
         <f>424*Assumptions!B24</f>
         <v>12720</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="36">
         <f>437*Assumptions!B25</f>
         <v>15732</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="36">
         <f>450*Assumptions!B26</f>
         <v>18000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="33">
+        <v>119</v>
+      </c>
+      <c r="B5" s="37">
         <f>SUM(B4:B4)</f>
         <v>6000</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="37">
         <f>SUM(C4:C4)</f>
         <v>9064</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="37">
         <f>SUM(D4:D4)</f>
         <v>12720</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="37">
         <f>SUM(E4:E4)</f>
         <v>15732</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="37">
         <f>SUM(F4:F4)</f>
         <v>18000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2552,57 +2638,57 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="32">
+        <v>121</v>
+      </c>
+      <c r="B7" s="36">
         <f>250*Assumptions!B22</f>
         <v>3750</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="36">
         <f>258*Assumptions!B23</f>
         <v>5676</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="36">
         <f>265*Assumptions!B24</f>
         <v>7950</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="36">
         <f>273*Assumptions!B25</f>
         <v>9828</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="36">
         <f>281*Assumptions!B26</f>
         <v>11240</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="33">
+        <v>122</v>
+      </c>
+      <c r="B8" s="37">
         <f>SUM(B7:B7)</f>
         <v>3750</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="37">
         <f>SUM(C7:C7)</f>
         <v>5676</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="37">
         <f>SUM(D7:D7)</f>
         <v>7950</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="37">
         <f>SUM(E7:E7)</f>
         <v>9828</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="37">
         <f>SUM(F7:F7)</f>
         <v>11240</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2612,120 +2698,120 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="32">
+        <v>124</v>
+      </c>
+      <c r="B10" s="36">
         <f>1800*12</f>
         <v>21600</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="36">
         <f>1854*12</f>
         <v>22248</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="36">
         <f>1910*12</f>
         <v>22920</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="36">
         <f>1967*12</f>
         <v>23604</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="36">
         <f>2026*12</f>
         <v>24312</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" s="32">
+        <v>125</v>
+      </c>
+      <c r="B11" s="36">
         <f>200*12</f>
         <v>2400</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="36">
         <f>205*12</f>
         <v>2460</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="36">
         <f>210*12</f>
         <v>2520</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="36">
         <f>215*12</f>
         <v>2580</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="36">
         <f>221*12</f>
         <v>2652</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="B12" s="32">
+        <v>126</v>
+      </c>
+      <c r="B12" s="36">
         <v>1800</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="36">
         <v>1845</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="36">
         <v>1891</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="36">
         <v>1938</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="36">
         <v>1987</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B13" s="33">
+        <v>127</v>
+      </c>
+      <c r="B13" s="37">
         <f>SUM(B10:B12)</f>
         <v>25800</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="37">
         <f>SUM(C10:C12)</f>
         <v>26553</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="37">
         <f>SUM(D10:D12)</f>
         <v>27331</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="37">
         <f>SUM(E10:E12)</f>
         <v>28122</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="37">
         <f>SUM(F10:F12)</f>
         <v>28951</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" s="33">
+        <v>128</v>
+      </c>
+      <c r="B15" s="37">
         <f>B5+B8+B13</f>
         <v>35550</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="37">
         <f>C5+C8+C13</f>
         <v>41293</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="37">
         <f>D5+D8+D13</f>
         <v>48001</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="37">
         <f>E5+E8+E13</f>
         <v>53682</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="37">
         <f>F5+F8+F13</f>
         <v>58191</v>
       </c>
@@ -2753,28 +2839,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>81</v>
+      <c r="B1" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2784,41 +2870,41 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="B3" s="32">
+        <v>130</v>
+      </c>
+      <c r="B3" s="36">
         <v>0</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="36">
         <v>0</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="36">
         <v>0</v>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="36">
         <v>0</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" s="33">
+        <v>131</v>
+      </c>
+      <c r="B4" s="37">
         <v>0</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="37">
         <v>0</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="37">
         <v>0</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="37">
         <v>0</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="37">
         <v>0</v>
       </c>
     </row>
@@ -2845,71 +2931,71 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>81</v>
+      <c r="B1" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="B2" s="32">
+        <v>132</v>
+      </c>
+      <c r="B2" s="36">
         <f>'Revenue Schedule'!B14</f>
         <v>201000</v>
       </c>
-      <c r="C2" s="32">
+      <c r="C2" s="36">
         <f>'Revenue Schedule'!C14</f>
         <v>302980</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2" s="36">
         <f>'Revenue Schedule'!D14</f>
         <v>424730</v>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="36">
         <f>'Revenue Schedule'!E14</f>
         <v>523580</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="36">
         <f>'Revenue Schedule'!F14</f>
         <v>598240</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="B3" s="32">
+        <v>133</v>
+      </c>
+      <c r="B3" s="36">
         <f>'Staffing &amp; Personnel'!B21</f>
         <v>64516</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="36">
         <f>'Staffing &amp; Personnel'!C21</f>
         <v>79742</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="36">
         <f>'Staffing &amp; Personnel'!D21</f>
         <v>82134</v>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="36">
         <f>'Staffing &amp; Personnel'!E21</f>
         <v>84598</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="36">
         <f>'Staffing &amp; Personnel'!F21</f>
         <v>87136</v>
       </c>
@@ -2918,23 +3004,23 @@
       <c r="A4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="36">
         <f>'Operating Expenses'!B15</f>
         <v>35550</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="36">
         <f>'Operating Expenses'!C15</f>
         <v>41293</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="36">
         <f>'Operating Expenses'!D15</f>
         <v>48001</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="36">
         <f>'Operating Expenses'!E15</f>
         <v>53682</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="36">
         <f>'Operating Expenses'!F15</f>
         <v>58191</v>
       </c>
@@ -2943,98 +3029,98 @@
       <c r="A5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="32" t="str">
+      <c r="B5" s="36" t="str">
         <f>'Capital &amp; Debt'!B4</f>
         <v>0</v>
       </c>
-      <c r="C5" s="32" t="str">
+      <c r="C5" s="36" t="str">
         <f>'Capital &amp; Debt'!C4</f>
         <v>0</v>
       </c>
-      <c r="D5" s="32" t="str">
+      <c r="D5" s="36" t="str">
         <f>'Capital &amp; Debt'!D4</f>
         <v>0</v>
       </c>
-      <c r="E5" s="32" t="str">
+      <c r="E5" s="36" t="str">
         <f>'Capital &amp; Debt'!E4</f>
         <v>0</v>
       </c>
-      <c r="F5" s="32" t="str">
+      <c r="F5" s="36" t="str">
         <f>'Capital &amp; Debt'!F4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="33">
+        <v>134</v>
+      </c>
+      <c r="B6" s="37">
         <f>B3+B4+B5</f>
         <v>100066</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="37">
         <f>C3+C4+C5</f>
         <v>121035</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="37">
         <f>D3+D4+D5</f>
         <v>130135</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="37">
         <f>E3+E4+E5</f>
         <v>138280</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="37">
         <f>F3+F4+F5</f>
         <v>145327</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="33">
+        <v>135</v>
+      </c>
+      <c r="B7" s="37">
         <f>B2-B6</f>
         <v>100934</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="37">
         <f>C2-C6</f>
         <v>181945</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="37">
         <f>D2-D6</f>
         <v>294595</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="37">
         <f>E2-E6</f>
         <v>385300</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="37">
         <f>F2-F6</f>
         <v>452913</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="32">
+        <v>136</v>
+      </c>
+      <c r="B8" s="36">
         <f>B7</f>
         <v>100934</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="36">
         <f>B8+C7</f>
         <v>282879</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="36">
         <f>C8+D7</f>
         <v>577474</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="36">
         <f>D8+E7</f>
         <v>962774</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="36">
         <f>E8+F7</f>
         <v>1415687</v>
       </c>
@@ -3043,44 +3129,44 @@
       <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="44">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>12.10409129974217</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="44">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>28.04600322220845</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="44">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>53.249994236754134</v>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="44">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>83.54995660977725</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="44">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>116.8966812773951</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="42" t="s">
+      <c r="A10" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="42" t="s">
+      <c r="F10" s="46" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3107,18 +3193,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
+      <c r="A1" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
-        <v>145</v>
+      <c r="A2" s="48" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3135,7 +3221,7 @@
       <c r="A5" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="27" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3143,7 +3229,7 @@
       <c r="A6" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="27" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3151,7 +3237,7 @@
       <c r="A7" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="27" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3159,7 +3245,7 @@
       <c r="A8" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="27" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3167,7 +3253,7 @@
       <c r="A9" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="27" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3175,7 +3261,7 @@
       <c r="A10" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3183,7 +3269,7 @@
       <c r="A11" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="27" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3191,13 +3277,13 @@
       <c r="A12" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>146</v>
+      <c r="B12" s="27" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3206,140 +3292,140 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="30" t="s">
-        <v>81</v>
+      <c r="B15" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="31">
+        <v>77</v>
+      </c>
+      <c r="B16" s="35">
         <f>'Revenue Schedule'!B2</f>
         <v>15</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="35">
         <f>'Revenue Schedule'!C2</f>
         <v>22</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="35">
         <f>'Revenue Schedule'!D2</f>
         <v>30</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="35">
         <f>'Revenue Schedule'!E2</f>
         <v>36</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="35">
         <f>'Revenue Schedule'!F2</f>
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C17" s="45">
+        <v>144</v>
+      </c>
+      <c r="C17" s="49">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.4666666666666667</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="49">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.36363636363636365</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="49">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.2</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="49">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="30" t="s">
-        <v>81</v>
+      <c r="B19" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="B20" s="32">
+        <v>132</v>
+      </c>
+      <c r="B20" s="36">
         <f>'Financial Model'!B2</f>
         <v>201000</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="36">
         <f>'Financial Model'!C2</f>
         <v>302980</v>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="36">
         <f>'Financial Model'!D2</f>
         <v>424730</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="36">
         <f>'Financial Model'!E2</f>
         <v>523580</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="36">
         <f>'Financial Model'!F2</f>
         <v>598240</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="B21" s="32">
+        <v>133</v>
+      </c>
+      <c r="B21" s="36">
         <f>'Financial Model'!B3</f>
         <v>64516</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="36">
         <f>'Financial Model'!C3</f>
         <v>79742</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="36">
         <f>'Financial Model'!D3</f>
         <v>82134</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="36">
         <f>'Financial Model'!E3</f>
         <v>84598</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="36">
         <f>'Financial Model'!F3</f>
         <v>87136</v>
       </c>
@@ -3348,104 +3434,104 @@
       <c r="A22" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="36">
         <f>'Financial Model'!B4</f>
         <v>35550</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="36">
         <f>'Financial Model'!C4</f>
         <v>41293</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="36">
         <f>'Financial Model'!D4</f>
         <v>48001</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="36">
         <f>'Financial Model'!E4</f>
         <v>53682</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="36">
         <f>'Financial Model'!F4</f>
         <v>58191</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B23" s="33">
+        <v>134</v>
+      </c>
+      <c r="B23" s="37">
         <f>'Financial Model'!B6</f>
         <v>100066</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="37">
         <f>'Financial Model'!C6</f>
         <v>121035</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="37">
         <f>'Financial Model'!D6</f>
         <v>130135</v>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="37">
         <f>'Financial Model'!E6</f>
         <v>138280</v>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="37">
         <f>'Financial Model'!F6</f>
         <v>145327</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="B24" s="46">
+      <c r="A24" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="50">
         <f>'Financial Model'!B7</f>
         <v>100934</v>
       </c>
-      <c r="C24" s="46">
+      <c r="C24" s="50">
         <f>'Financial Model'!C7</f>
         <v>181945</v>
       </c>
-      <c r="D24" s="46">
+      <c r="D24" s="50">
         <f>'Financial Model'!D7</f>
         <v>294595</v>
       </c>
-      <c r="E24" s="46">
+      <c r="E24" s="50">
         <f>'Financial Model'!E7</f>
         <v>385300</v>
       </c>
-      <c r="F24" s="46">
+      <c r="F24" s="50">
         <f>'Financial Model'!F7</f>
         <v>452913</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="B25" s="32">
+        <v>136</v>
+      </c>
+      <c r="B25" s="36">
         <f>'Financial Model'!B8</f>
         <v>100934</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="36">
         <f>'Financial Model'!C8</f>
         <v>282879</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="36">
         <f>'Financial Model'!D8</f>
         <v>577474</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="36">
         <f>'Financial Model'!E8</f>
         <v>962774</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="36">
         <f>'Financial Model'!F8</f>
         <v>1415687</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="27" t="s">
         <v>11</v>
       </c>
       <c r="B26" s="13">
@@ -3471,7 +3557,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3481,82 +3567,82 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B29" s="32">
+        <v>146</v>
+      </c>
+      <c r="B29" s="36">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>13400</v>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="36">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>13771.818181818182</v>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="36">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>14157.666666666666</v>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="36">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>14543.888888888889</v>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="36">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>14956</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="B30" s="45">
+        <v>147</v>
+      </c>
+      <c r="B30" s="49">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.32097512437810943</v>
       </c>
-      <c r="C30" s="45">
+      <c r="C30" s="49">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.2631922899201267</v>
       </c>
-      <c r="D30" s="45">
+      <c r="D30" s="49">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.19337932333482447</v>
       </c>
-      <c r="E30" s="45">
+      <c r="E30" s="49">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.16157607242446237</v>
       </c>
-      <c r="F30" s="45">
+      <c r="F30" s="49">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.1456539181599358</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="B31" s="45">
+        <v>148</v>
+      </c>
+      <c r="B31" s="49">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.17686567164179104</v>
       </c>
-      <c r="C31" s="45">
+      <c r="C31" s="49">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.13628952406099412</v>
       </c>
-      <c r="D31" s="45">
+      <c r="D31" s="49">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.11301532738445601</v>
       </c>
-      <c r="E31" s="45">
+      <c r="E31" s="49">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.10252874441346117</v>
       </c>
-      <c r="F31" s="45">
+      <c r="F31" s="49">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.09727032629045199</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
-        <v>154</v>
+      <c r="A32" s="27" t="s">
+        <v>149</v>
       </c>
       <c r="B32" s="12">
         <f>IF(B20=0,0,B24/B20)</f>
@@ -3581,7 +3667,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3591,61 +3677,61 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="B35" s="45">
+        <v>151</v>
+      </c>
+      <c r="B35" s="49">
         <v>0.4626865671641791</v>
       </c>
-      <c r="C35" s="45">
+      <c r="C35" s="49">
         <v>0.46326490197372766</v>
       </c>
-      <c r="D35" s="45">
+      <c r="D35" s="49">
         <v>0.46370635462529136</v>
       </c>
-      <c r="E35" s="45">
+      <c r="E35" s="49">
         <v>0.4645250009549639</v>
       </c>
-      <c r="F35" s="45">
+      <c r="F35" s="49">
         <v>0.4648970312917893</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="B36" s="45">
+        <v>152</v>
+      </c>
+      <c r="B36" s="49">
         <v>0.5223880597014925</v>
       </c>
-      <c r="C36" s="45">
+      <c r="C36" s="49">
         <v>0.5235329064624727</v>
       </c>
-      <c r="D36" s="45">
+      <c r="D36" s="49">
         <v>0.5245214606926754</v>
       </c>
-      <c r="E36" s="45">
+      <c r="E36" s="49">
         <v>0.5259253600213912</v>
       </c>
-      <c r="F36" s="45">
+      <c r="F36" s="49">
         <v>0.5267451190157796</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="B37" s="45">
+        <v>153</v>
+      </c>
+      <c r="B37" s="49">
         <v>0.014925373134328358</v>
       </c>
-      <c r="C37" s="45">
+      <c r="C37" s="49">
         <v>0.01320219156379959</v>
       </c>
-      <c r="D37" s="45">
+      <c r="D37" s="49">
         <v>0.011772184682033292</v>
       </c>
-      <c r="E37" s="45">
+      <c r="E37" s="49">
         <v>0.009549639023644906</v>
       </c>
-      <c r="F37" s="45">
+      <c r="F37" s="49">
         <v>0.008357849692431132</v>
       </c>
     </row>
@@ -3858,118 +3944,118 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="43" t="s">
-        <v>159</v>
-      </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="B3" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="50" t="s">
-        <v>163</v>
+      <c r="B4" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="51" t="s">
-        <v>165</v>
+        <v>159</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" s="52">
+        <v>161</v>
+      </c>
+      <c r="C7" s="56">
         <v>15</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="56">
         <v>22</v>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="56">
         <v>30</v>
       </c>
-      <c r="F7" s="52">
+      <c r="F7" s="56">
         <v>36</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="56">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C8" s="53">
+        <v>162</v>
+      </c>
+      <c r="C8" s="57">
         <v>201000</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="57">
         <v>302980</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="57">
         <v>424730</v>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="57">
         <v>523580</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="57">
         <v>598240</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" s="53">
+        <v>163</v>
+      </c>
+      <c r="C9" s="57">
         <v>64516</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="57">
         <v>79742</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="57">
         <v>82134</v>
       </c>
-      <c r="F9" s="53">
+      <c r="F9" s="57">
         <v>84598</v>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="57">
         <v>87136</v>
       </c>
     </row>
@@ -3977,431 +4063,431 @@
       <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="57">
         <v>35550</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="57">
         <v>41293</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="57">
         <v>48001</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="57">
         <v>53682</v>
       </c>
-      <c r="G10" s="53">
+      <c r="G10" s="57">
         <v>58191</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="57">
+        <v>0</v>
+      </c>
+      <c r="D11" s="57">
+        <v>0</v>
+      </c>
+      <c r="E11" s="57">
+        <v>0</v>
+      </c>
+      <c r="F11" s="57">
+        <v>0</v>
+      </c>
+      <c r="G11" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="59">
+        <v>100934</v>
+      </c>
+      <c r="D12" s="59">
+        <v>181945</v>
+      </c>
+      <c r="E12" s="59">
+        <v>294595</v>
+      </c>
+      <c r="F12" s="59">
+        <v>385300</v>
+      </c>
+      <c r="G12" s="59">
+        <v>452913</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="58" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="59">
+        <v>100934</v>
+      </c>
+      <c r="D13" s="59">
+        <v>282879</v>
+      </c>
+      <c r="E13" s="59">
+        <v>577474</v>
+      </c>
+      <c r="F13" s="59">
+        <v>962774</v>
+      </c>
+      <c r="G13" s="59">
+        <v>1415687</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="C14" s="60">
+        <v>0.5021592039800995</v>
+      </c>
+      <c r="D14" s="60">
+        <v>0.6005181860188792</v>
+      </c>
+      <c r="E14" s="60">
+        <v>0.6936053492807195</v>
+      </c>
+      <c r="F14" s="60">
+        <v>0.7358951831620765</v>
+      </c>
+      <c r="G14" s="60">
+        <v>0.7570757555496122</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" s="61">
+        <v>13400</v>
+      </c>
+      <c r="D15" s="61">
+        <v>13771.818181818182</v>
+      </c>
+      <c r="E15" s="61">
+        <v>14157.666666666666</v>
+      </c>
+      <c r="F15" s="61">
+        <v>14543.888888888889</v>
+      </c>
+      <c r="G15" s="61">
+        <v>14956</v>
+      </c>
+      <c r="H15" s="62" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="53">
-        <v>0</v>
-      </c>
-      <c r="D11" s="53">
-        <v>0</v>
-      </c>
-      <c r="E11" s="53">
-        <v>0</v>
-      </c>
-      <c r="F11" s="53">
-        <v>0</v>
-      </c>
-      <c r="G11" s="53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="54" t="s">
+      <c r="C16" s="60">
+        <v>0.32097512437810943</v>
+      </c>
+      <c r="D16" s="60">
+        <v>0.2631922899201267</v>
+      </c>
+      <c r="E16" s="60">
+        <v>0.19337932333482447</v>
+      </c>
+      <c r="F16" s="60">
+        <v>0.16157607242446237</v>
+      </c>
+      <c r="G16" s="60">
+        <v>0.1456539181599358</v>
+      </c>
+      <c r="H16" s="62" t="s">
         <v>170</v>
       </c>
-      <c r="C12" s="55">
-        <v>100934</v>
-      </c>
-      <c r="D12" s="55">
-        <v>181945</v>
-      </c>
-      <c r="E12" s="55">
-        <v>294595</v>
-      </c>
-      <c r="F12" s="55">
-        <v>385300</v>
-      </c>
-      <c r="G12" s="55">
-        <v>452913</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="54" t="s">
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="58" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="55">
-        <v>100934</v>
-      </c>
-      <c r="D13" s="55">
-        <v>282879</v>
-      </c>
-      <c r="E13" s="55">
-        <v>577474</v>
-      </c>
-      <c r="F13" s="55">
-        <v>962774</v>
-      </c>
-      <c r="G13" s="55">
-        <v>1415687</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="54" t="s">
+      <c r="C17" s="60">
+        <v>0.12835820895522387</v>
+      </c>
+      <c r="D17" s="60">
+        <v>0.08763944814839263</v>
+      </c>
+      <c r="E17" s="60">
+        <v>0.06433837967650036</v>
+      </c>
+      <c r="F17" s="60">
+        <v>0.05370889491577219</v>
+      </c>
+      <c r="G17" s="60">
+        <v>0.048391933498261576</v>
+      </c>
+      <c r="H17" s="62" t="s">
         <v>172</v>
       </c>
-      <c r="C14" s="56">
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="60">
         <v>0.5021592039800995</v>
       </c>
-      <c r="D14" s="56">
+      <c r="D18" s="60">
         <v>0.6005181860188792</v>
       </c>
-      <c r="E14" s="56">
+      <c r="E18" s="60">
         <v>0.6936053492807195</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F18" s="60">
         <v>0.7358951831620765</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G18" s="60">
         <v>0.7570757555496122</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="54" t="s">
-        <v>151</v>
-      </c>
-      <c r="C15" s="57">
-        <v>13400</v>
-      </c>
-      <c r="D15" s="57">
-        <v>13771.818181818182</v>
-      </c>
-      <c r="E15" s="57">
-        <v>14157.666666666666</v>
-      </c>
-      <c r="F15" s="57">
-        <v>14543.888888888889</v>
-      </c>
-      <c r="G15" s="57">
-        <v>14956</v>
-      </c>
-      <c r="H15" s="58" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="54" t="s">
+      <c r="H18" s="62" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="56">
-        <v>0.32097512437810943</v>
-      </c>
-      <c r="D16" s="56">
-        <v>0.2631922899201267</v>
-      </c>
-      <c r="E16" s="56">
-        <v>0.19337932333482447</v>
-      </c>
-      <c r="F16" s="56">
-        <v>0.16157607242446237</v>
-      </c>
-      <c r="G16" s="56">
-        <v>0.1456539181599358</v>
-      </c>
-      <c r="H16" s="58" t="s">
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="58" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="54" t="s">
+      <c r="C19" s="63">
+        <v>3</v>
+      </c>
+      <c r="D19" s="63">
+        <v>3</v>
+      </c>
+      <c r="E19" s="63">
+        <v>3</v>
+      </c>
+      <c r="F19" s="63">
+        <v>3</v>
+      </c>
+      <c r="G19" s="63">
+        <v>3</v>
+      </c>
+      <c r="H19" s="62" t="s">
         <v>176</v>
       </c>
-      <c r="C17" s="56">
-        <v>0.12835820895522387</v>
-      </c>
-      <c r="D17" s="56">
-        <v>0.08763944814839263</v>
-      </c>
-      <c r="E17" s="56">
-        <v>0.06433837967650036</v>
-      </c>
-      <c r="F17" s="56">
-        <v>0.05370889491577219</v>
-      </c>
-      <c r="G17" s="56">
-        <v>0.048391933498261576</v>
-      </c>
-      <c r="H17" s="58" t="s">
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="58" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="54" t="s">
+      <c r="C20" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="56">
-        <v>0.5021592039800995</v>
-      </c>
-      <c r="D18" s="56">
-        <v>0.6005181860188792</v>
-      </c>
-      <c r="E18" s="56">
-        <v>0.6936053492807195</v>
-      </c>
-      <c r="F18" s="56">
-        <v>0.7358951831620765</v>
-      </c>
-      <c r="G18" s="56">
-        <v>0.7570757555496122</v>
-      </c>
-      <c r="H18" s="58" t="s">
+      <c r="D20" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="G20" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="H20" s="62" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="58" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="54" t="s">
-        <v>180</v>
-      </c>
-      <c r="C19" s="59">
-        <v>3</v>
-      </c>
-      <c r="D19" s="59">
-        <v>3</v>
-      </c>
-      <c r="E19" s="59">
-        <v>3</v>
-      </c>
-      <c r="F19" s="59">
-        <v>3</v>
-      </c>
-      <c r="G19" s="59">
-        <v>3</v>
-      </c>
-      <c r="H19" s="58" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="C20" s="60" t="s">
-        <v>183</v>
-      </c>
-      <c r="D20" s="60" t="s">
-        <v>183</v>
-      </c>
-      <c r="E20" s="60" t="s">
-        <v>183</v>
-      </c>
-      <c r="F20" s="60" t="s">
-        <v>183</v>
-      </c>
-      <c r="G20" s="60" t="s">
-        <v>183</v>
-      </c>
-      <c r="H20" s="58" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="54" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="41" t="str">
+      <c r="C21" s="45" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="61" t="str">
+      <c r="D21" s="65" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="61" t="str">
+      <c r="E21" s="65" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="61" t="str">
+      <c r="F21" s="65" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="61" t="str">
+      <c r="G21" s="65" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="58" t="s">
-        <v>77</v>
+      <c r="H21" s="62" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="C22" s="62">
+      <c r="B22" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="66">
         <v>12</v>
       </c>
-      <c r="D22" s="59">
+      <c r="D22" s="63">
         <v>28</v>
       </c>
-      <c r="E22" s="59">
+      <c r="E22" s="63">
         <v>53</v>
       </c>
-      <c r="F22" s="63" t="s">
-        <v>186</v>
-      </c>
-      <c r="G22" s="63" t="s">
-        <v>186</v>
-      </c>
-      <c r="H22" s="58" t="s">
-        <v>187</v>
+      <c r="F22" s="67" t="s">
+        <v>181</v>
+      </c>
+      <c r="G22" s="67" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="62" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="64" t="s">
+      <c r="B25" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="69" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="69"/>
+      <c r="F25" s="70" t="s">
+        <v>190</v>
+      </c>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="C26" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="69" t="s">
         <v>192</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="E26" s="69"/>
+      <c r="F26" s="70" t="s">
         <v>193</v>
       </c>
-      <c r="D25" s="65" t="s">
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="68" t="s">
         <v>194</v>
       </c>
-      <c r="E25" s="65"/>
-      <c r="F25" s="66" t="s">
+      <c r="C27" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="69" t="s">
         <v>195</v>
       </c>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="64" t="s">
+      <c r="E27" s="69"/>
+      <c r="F27" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="C26" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="D26" s="65" t="s">
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="68" t="s">
         <v>197</v>
       </c>
-      <c r="E26" s="65"/>
-      <c r="F26" s="66" t="s">
+      <c r="C28" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="69" t="s">
         <v>198</v>
       </c>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="64" t="s">
+      <c r="E28" s="69"/>
+      <c r="F28" s="70" t="s">
         <v>199</v>
       </c>
-      <c r="C27" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="D27" s="65" t="s">
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="E27" s="65"/>
-      <c r="F27" s="66" t="s">
+      <c r="C29" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="69" t="s">
         <v>201</v>
       </c>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="64" t="s">
+      <c r="E29" s="69"/>
+      <c r="F29" s="70" t="s">
         <v>202</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="65" t="s">
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="68" t="s">
         <v>203</v>
       </c>
-      <c r="E28" s="65"/>
-      <c r="F28" s="66" t="s">
+      <c r="C30" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="64" t="s">
+      <c r="E30" s="69"/>
+      <c r="F30" s="70" t="s">
         <v>205</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="D29" s="65" t="s">
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="58" t="s">
         <v>206</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="66" t="s">
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="71" t="s">
         <v>207</v>
       </c>
-      <c r="G29" s="66"/>
-      <c r="H29" s="66"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="64" t="s">
-        <v>208</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="D30" s="65" t="s">
-        <v>209</v>
-      </c>
-      <c r="E30" s="65"/>
-      <c r="F30" s="66" t="s">
-        <v>210</v>
-      </c>
-      <c r="G30" s="66"/>
-      <c r="H30" s="66"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="64" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="54" t="s">
-        <v>211</v>
-      </c>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="67" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="67"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="67"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="67"/>
-      <c r="H34" s="67"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="210">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -586,6 +586,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -3933,7 +3939,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4348,153 +4354,174 @@
         <v>182</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="58" t="s">
         <v>183</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C23" s="63">
+        <v>368</v>
+      </c>
+      <c r="D23" s="63">
+        <v>853</v>
+      </c>
+      <c r="E23" s="63">
+        <v>1620</v>
+      </c>
+      <c r="F23" s="63">
+        <v>2541</v>
+      </c>
+      <c r="G23" s="63">
+        <v>3556</v>
+      </c>
+      <c r="H23" s="62" t="s">
         <v>184</v>
       </c>
-      <c r="D24" s="8" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="68" t="s">
+      <c r="D25" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C25" s="45" t="s">
+      <c r="E25" s="8"/>
+      <c r="F25" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="69" t="s">
-        <v>189</v>
-      </c>
-      <c r="E25" s="69"/>
-      <c r="F25" s="70" t="s">
-        <v>190</v>
-      </c>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="69" t="s">
         <v>191</v>
-      </c>
-      <c r="C26" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="D26" s="69" t="s">
-        <v>192</v>
       </c>
       <c r="E26" s="69"/>
       <c r="F26" s="70" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G26" s="70"/>
       <c r="H26" s="70"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" s="69" t="s">
         <v>194</v>
-      </c>
-      <c r="C27" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="D27" s="69" t="s">
-        <v>195</v>
       </c>
       <c r="E27" s="69"/>
       <c r="F27" s="70" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G27" s="70"/>
       <c r="H27" s="70"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="69" t="s">
         <v>197</v>
-      </c>
-      <c r="C28" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="D28" s="69" t="s">
-        <v>198</v>
       </c>
       <c r="E28" s="69"/>
       <c r="F28" s="70" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G28" s="70"/>
       <c r="H28" s="70"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="68" t="s">
+        <v>199</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="69" t="s">
         <v>200</v>
-      </c>
-      <c r="C29" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="D29" s="69" t="s">
-        <v>201</v>
       </c>
       <c r="E29" s="69"/>
       <c r="F29" s="70" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G29" s="70"/>
       <c r="H29" s="70"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="69" t="s">
         <v>203</v>
-      </c>
-      <c r="C30" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="D30" s="69" t="s">
-        <v>204</v>
       </c>
       <c r="E30" s="69"/>
       <c r="F30" s="70" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G30" s="70"/>
       <c r="H30" s="70"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="68" t="s">
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="C31" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="E31" s="69"/>
+      <c r="F31" s="70" t="s">
+        <v>207</v>
+      </c>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="58" t="s">
-        <v>206</v>
-      </c>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="71" t="s">
-        <v>207</v>
-      </c>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="C33" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="D33" s="58"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="58"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -4507,8 +4534,10 @@
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="215">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -544,6 +544,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -921,7 +936,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1005,6 +1020,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3939,7 +3960,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4188,356 +4209,439 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="60">
-        <v>0.32097512437810943</v>
-      </c>
-      <c r="D16" s="60">
-        <v>0.2631922899201267</v>
-      </c>
-      <c r="E16" s="60">
-        <v>0.19337932333482447</v>
-      </c>
-      <c r="F16" s="60">
-        <v>0.16157607242446237</v>
-      </c>
-      <c r="G16" s="60">
-        <v>0.1456539181599358</v>
-      </c>
-      <c r="H16" s="62" t="s">
+      <c r="C16" s="63">
+        <v>6671.066666666667</v>
+      </c>
+      <c r="D16" s="63">
+        <v>5501.590909090909</v>
+      </c>
+      <c r="E16" s="63">
+        <v>4337.833333333333</v>
+      </c>
+      <c r="F16" s="63">
+        <v>3841.1111111111113</v>
+      </c>
+      <c r="G16" s="63">
+        <v>3633.175</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="58" t="s">
+      <c r="C17" s="57">
+        <v>400</v>
+      </c>
+      <c r="D17" s="57">
+        <v>412</v>
+      </c>
+      <c r="E17" s="57">
+        <v>424</v>
+      </c>
+      <c r="F17" s="57">
+        <v>437</v>
+      </c>
+      <c r="G17" s="57">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C17" s="60">
-        <v>0.12835820895522387</v>
-      </c>
-      <c r="D17" s="60">
-        <v>0.08763944814839263</v>
-      </c>
-      <c r="E17" s="60">
-        <v>0.06433837967650036</v>
-      </c>
-      <c r="F17" s="60">
-        <v>0.05370889491577219</v>
-      </c>
-      <c r="G17" s="60">
-        <v>0.048391933498261576</v>
-      </c>
-      <c r="H17" s="62" t="s">
+      <c r="C18" s="61">
+        <v>1720</v>
+      </c>
+      <c r="D18" s="61">
+        <v>1206.9545454545455</v>
+      </c>
+      <c r="E18" s="61">
+        <v>910.8813333333333</v>
+      </c>
+      <c r="F18" s="61">
+        <v>781.1362</v>
+      </c>
+      <c r="G18" s="61">
+        <v>723.7497574000001</v>
+      </c>
+      <c r="H18" s="62" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="58" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="C18" s="60">
-        <v>0.5021592039800995</v>
-      </c>
-      <c r="D18" s="60">
-        <v>0.6005181860188792</v>
-      </c>
-      <c r="E18" s="60">
-        <v>0.6936053492807195</v>
-      </c>
-      <c r="F18" s="60">
-        <v>0.7358951831620765</v>
-      </c>
-      <c r="G18" s="60">
-        <v>0.7570757555496122</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="58" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" s="63">
-        <v>3</v>
-      </c>
-      <c r="D19" s="63">
-        <v>3</v>
-      </c>
-      <c r="E19" s="63">
-        <v>3</v>
-      </c>
-      <c r="F19" s="63">
-        <v>3</v>
-      </c>
-      <c r="G19" s="63">
-        <v>3</v>
-      </c>
-      <c r="H19" s="62" t="s">
-        <v>176</v>
+      <c r="C19" s="64">
+        <v>6728.933333333333</v>
+      </c>
+      <c r="D19" s="64">
+        <v>8270.227272727272</v>
+      </c>
+      <c r="E19" s="64">
+        <v>9819.833333333334</v>
+      </c>
+      <c r="F19" s="64">
+        <v>10702.777777777777</v>
+      </c>
+      <c r="G19" s="64">
+        <v>11322.825</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="D20" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="E20" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="F20" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="G20" s="64" t="s">
-        <v>178</v>
+        <v>174</v>
+      </c>
+      <c r="C20" s="60">
+        <v>0.32097512437810943</v>
+      </c>
+      <c r="D20" s="60">
+        <v>0.2631922899201267</v>
+      </c>
+      <c r="E20" s="60">
+        <v>0.19337932333482447</v>
+      </c>
+      <c r="F20" s="60">
+        <v>0.16157607242446237</v>
+      </c>
+      <c r="G20" s="60">
+        <v>0.1456539181599358</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="60">
+        <v>0.12835820895522387</v>
+      </c>
+      <c r="D21" s="60">
+        <v>0.08763944814839263</v>
+      </c>
+      <c r="E21" s="60">
+        <v>0.06433837967650036</v>
+      </c>
+      <c r="F21" s="60">
+        <v>0.05370889491577219</v>
+      </c>
+      <c r="G21" s="60">
+        <v>0.048391933498261576</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="58" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="60">
+        <v>0.5021592039800995</v>
+      </c>
+      <c r="D22" s="60">
+        <v>0.6005181860188792</v>
+      </c>
+      <c r="E22" s="60">
+        <v>0.6936053492807195</v>
+      </c>
+      <c r="F22" s="60">
+        <v>0.7358951831620765</v>
+      </c>
+      <c r="G22" s="60">
+        <v>0.7570757555496122</v>
+      </c>
+      <c r="H22" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="C21" s="45" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" s="65">
+        <v>3</v>
+      </c>
+      <c r="D23" s="65">
+        <v>3</v>
+      </c>
+      <c r="E23" s="65">
+        <v>3</v>
+      </c>
+      <c r="F23" s="65">
+        <v>3</v>
+      </c>
+      <c r="G23" s="65">
+        <v>3</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="C24" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="D24" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="F24" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="G24" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="C25" s="45" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="65" t="str">
+      <c r="D25" s="67" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="65" t="str">
+      <c r="E25" s="67" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="65" t="str">
+      <c r="F25" s="67" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="65" t="str">
+      <c r="G25" s="67" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="62" t="s">
+      <c r="H25" s="62" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="C22" s="66">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="68">
         <v>12</v>
       </c>
-      <c r="D22" s="63">
+      <c r="D26" s="65">
         <v>28</v>
       </c>
-      <c r="E22" s="63">
+      <c r="E26" s="65">
         <v>53</v>
       </c>
-      <c r="F22" s="67" t="s">
-        <v>181</v>
-      </c>
-      <c r="G22" s="67" t="s">
-        <v>181</v>
-      </c>
-      <c r="H22" s="62" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="58" t="s">
-        <v>183</v>
-      </c>
-      <c r="C23" s="63">
+      <c r="F26" s="69" t="s">
+        <v>186</v>
+      </c>
+      <c r="G26" s="69" t="s">
+        <v>186</v>
+      </c>
+      <c r="H26" s="62" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="58" t="s">
+        <v>188</v>
+      </c>
+      <c r="C27" s="65">
         <v>368</v>
       </c>
-      <c r="D23" s="63">
+      <c r="D27" s="65">
         <v>853</v>
       </c>
-      <c r="E23" s="63">
+      <c r="E27" s="65">
         <v>1620</v>
       </c>
-      <c r="F23" s="63">
+      <c r="F27" s="65">
         <v>2541</v>
       </c>
-      <c r="G23" s="63">
+      <c r="G27" s="65">
         <v>3556</v>
       </c>
-      <c r="H23" s="62" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="68" t="s">
+      <c r="H27" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="C26" s="45" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D26" s="69" t="s">
+      <c r="C29" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="E26" s="69"/>
-      <c r="F26" s="70" t="s">
+      <c r="D29" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="68" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C27" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="D27" s="69" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="70" t="s">
         <v>194</v>
       </c>
-      <c r="E27" s="69"/>
-      <c r="F27" s="70" t="s">
+      <c r="C30" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="68" t="s">
+      <c r="D30" s="71" t="s">
         <v>196</v>
       </c>
-      <c r="C28" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="D28" s="69" t="s">
+      <c r="E30" s="71"/>
+      <c r="F30" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="E28" s="69"/>
-      <c r="F28" s="70" t="s">
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="70" t="s">
         <v>198</v>
       </c>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="68" t="s">
+      <c r="C31" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="71" t="s">
         <v>199</v>
       </c>
-      <c r="C29" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="D29" s="69" t="s">
+      <c r="E31" s="71"/>
+      <c r="F31" s="72" t="s">
         <v>200</v>
       </c>
-      <c r="E29" s="69"/>
-      <c r="F29" s="70" t="s">
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="70" t="s">
         <v>201</v>
       </c>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="68" t="s">
+      <c r="C32" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D32" s="71" t="s">
         <v>202</v>
       </c>
-      <c r="C30" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="D30" s="69" t="s">
+      <c r="E32" s="71"/>
+      <c r="F32" s="72" t="s">
         <v>203</v>
       </c>
-      <c r="E30" s="69"/>
-      <c r="F30" s="70" t="s">
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="70" t="s">
         <v>204</v>
       </c>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="68" t="s">
+      <c r="C33" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33" s="71" t="s">
         <v>205</v>
       </c>
-      <c r="C31" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="69" t="s">
+      <c r="E33" s="71"/>
+      <c r="F33" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="E31" s="69"/>
-      <c r="F31" s="70" t="s">
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="68" t="s">
+      <c r="C34" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34" s="71" t="s">
+        <v>208</v>
+      </c>
+      <c r="E34" s="71"/>
+      <c r="F34" s="72" t="s">
+        <v>209</v>
+      </c>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="70" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="E35" s="71"/>
+      <c r="F35" s="72" t="s">
+        <v>212</v>
+      </c>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="58" t="s">
-        <v>208</v>
-      </c>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="71" t="s">
-        <v>209</v>
-      </c>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
+      <c r="C37" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="73" t="s">
+        <v>214</v>
+      </c>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4583,37 +4687,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="208">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -546,21 +546,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -601,12 +586,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>Days Cash on Hand</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -936,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1020,12 +999,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3960,7 +3933,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4209,439 +4182,333 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="63">
-        <v>6671.066666666667</v>
-      </c>
-      <c r="D16" s="63">
-        <v>5501.590909090909</v>
-      </c>
-      <c r="E16" s="63">
-        <v>4337.833333333333</v>
-      </c>
-      <c r="F16" s="63">
-        <v>3841.1111111111113</v>
-      </c>
-      <c r="G16" s="63">
-        <v>3633.175</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="C16" s="60">
+        <v>0.32097512437810943</v>
+      </c>
+      <c r="D16" s="60">
+        <v>0.2631922899201267</v>
+      </c>
+      <c r="E16" s="60">
+        <v>0.19337932333482447</v>
+      </c>
+      <c r="F16" s="60">
+        <v>0.16157607242446237</v>
+      </c>
+      <c r="G16" s="60">
+        <v>0.1456539181599358</v>
+      </c>
+      <c r="H16" s="62" t="s">
         <v>170</v>
       </c>
-      <c r="C17" s="57">
-        <v>400</v>
-      </c>
-      <c r="D17" s="57">
-        <v>412</v>
-      </c>
-      <c r="E17" s="57">
-        <v>424</v>
-      </c>
-      <c r="F17" s="57">
-        <v>437</v>
-      </c>
-      <c r="G17" s="57">
-        <v>450</v>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="58" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" s="60">
+        <v>0.12835820895522387</v>
+      </c>
+      <c r="D17" s="60">
+        <v>0.08763944814839263</v>
+      </c>
+      <c r="E17" s="60">
+        <v>0.06433837967650036</v>
+      </c>
+      <c r="F17" s="60">
+        <v>0.05370889491577219</v>
+      </c>
+      <c r="G17" s="60">
+        <v>0.048391933498261576</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C18" s="61">
-        <v>1720</v>
-      </c>
-      <c r="D18" s="61">
-        <v>1206.9545454545455</v>
-      </c>
-      <c r="E18" s="61">
-        <v>910.8813333333333</v>
-      </c>
-      <c r="F18" s="61">
-        <v>781.1362</v>
-      </c>
-      <c r="G18" s="61">
-        <v>723.7497574000001</v>
+      <c r="B18" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="60">
+        <v>0.5021592039800995</v>
+      </c>
+      <c r="D18" s="60">
+        <v>0.6005181860188792</v>
+      </c>
+      <c r="E18" s="60">
+        <v>0.6936053492807195</v>
+      </c>
+      <c r="F18" s="60">
+        <v>0.7358951831620765</v>
+      </c>
+      <c r="G18" s="60">
+        <v>0.7570757555496122</v>
       </c>
       <c r="H18" s="62" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="58" t="s">
-        <v>173</v>
-      </c>
-      <c r="C19" s="64">
-        <v>6728.933333333333</v>
-      </c>
-      <c r="D19" s="64">
-        <v>8270.227272727272</v>
-      </c>
-      <c r="E19" s="64">
-        <v>9819.833333333334</v>
-      </c>
-      <c r="F19" s="64">
-        <v>10702.777777777777</v>
-      </c>
-      <c r="G19" s="64">
-        <v>11322.825</v>
+        <v>175</v>
+      </c>
+      <c r="C19" s="63">
+        <v>3</v>
+      </c>
+      <c r="D19" s="63">
+        <v>3</v>
+      </c>
+      <c r="E19" s="63">
+        <v>3</v>
+      </c>
+      <c r="F19" s="63">
+        <v>3</v>
+      </c>
+      <c r="G19" s="63">
+        <v>3</v>
+      </c>
+      <c r="H19" s="62" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="58" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" s="60">
-        <v>0.32097512437810943</v>
-      </c>
-      <c r="D20" s="60">
-        <v>0.2631922899201267</v>
-      </c>
-      <c r="E20" s="60">
-        <v>0.19337932333482447</v>
-      </c>
-      <c r="F20" s="60">
-        <v>0.16157607242446237</v>
-      </c>
-      <c r="G20" s="60">
-        <v>0.1456539181599358</v>
+        <v>177</v>
+      </c>
+      <c r="C20" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="G20" s="64" t="s">
+        <v>178</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="58" t="s">
-        <v>176</v>
-      </c>
-      <c r="C21" s="60">
-        <v>0.12835820895522387</v>
-      </c>
-      <c r="D21" s="60">
-        <v>0.08763944814839263</v>
-      </c>
-      <c r="E21" s="60">
-        <v>0.06433837967650036</v>
-      </c>
-      <c r="F21" s="60">
-        <v>0.05370889491577219</v>
-      </c>
-      <c r="G21" s="60">
-        <v>0.048391933498261576</v>
+        <v>179</v>
+      </c>
+      <c r="C21" s="45" t="str">
+        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="65" t="str">
+        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="65" t="str">
+        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="65" t="str">
+        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="65" t="str">
+        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="62" t="s">
-        <v>177</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="58" t="s">
-        <v>178</v>
-      </c>
-      <c r="C22" s="60">
-        <v>0.5021592039800995</v>
-      </c>
-      <c r="D22" s="60">
-        <v>0.6005181860188792</v>
-      </c>
-      <c r="E22" s="60">
-        <v>0.6936053492807195</v>
-      </c>
-      <c r="F22" s="60">
-        <v>0.7358951831620765</v>
-      </c>
-      <c r="G22" s="60">
-        <v>0.7570757555496122</v>
+        <v>180</v>
+      </c>
+      <c r="C22" s="66">
+        <v>12</v>
+      </c>
+      <c r="D22" s="63">
+        <v>28</v>
+      </c>
+      <c r="E22" s="63">
+        <v>53</v>
+      </c>
+      <c r="F22" s="67" t="s">
+        <v>181</v>
+      </c>
+      <c r="G22" s="67" t="s">
+        <v>181</v>
       </c>
       <c r="H22" s="62" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="C23" s="65">
-        <v>3</v>
-      </c>
-      <c r="D23" s="65">
-        <v>3</v>
-      </c>
-      <c r="E23" s="65">
-        <v>3</v>
-      </c>
-      <c r="F23" s="65">
-        <v>3</v>
-      </c>
-      <c r="G23" s="65">
-        <v>3</v>
-      </c>
-      <c r="H23" s="62" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="C24" s="66" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D24" s="66" t="s">
-        <v>183</v>
-      </c>
-      <c r="E24" s="66" t="s">
-        <v>183</v>
-      </c>
-      <c r="F24" s="66" t="s">
-        <v>183</v>
-      </c>
-      <c r="G24" s="66" t="s">
-        <v>183</v>
-      </c>
-      <c r="H24" s="62" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="58" t="s">
+      <c r="C24" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C25" s="45" t="str">
-        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="D25" s="67" t="str">
-        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="67" t="str">
-        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="67" t="str">
-        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="67" t="str">
-        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="58" t="s">
+      <c r="D24" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="C26" s="68">
-        <v>12</v>
-      </c>
-      <c r="D26" s="65">
-        <v>28</v>
-      </c>
-      <c r="E26" s="65">
-        <v>53</v>
-      </c>
-      <c r="F26" s="69" t="s">
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="G26" s="69" t="s">
-        <v>186</v>
-      </c>
-      <c r="H26" s="62" t="s">
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="68" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="58" t="s">
+      <c r="C25" s="45" t="s">
         <v>188</v>
       </c>
-      <c r="C27" s="65">
-        <v>368</v>
-      </c>
-      <c r="D27" s="65">
-        <v>853</v>
-      </c>
-      <c r="E27" s="65">
-        <v>1620</v>
-      </c>
-      <c r="F27" s="65">
-        <v>2541</v>
-      </c>
-      <c r="G27" s="65">
-        <v>3556</v>
-      </c>
-      <c r="H27" s="62" t="s">
+      <c r="D25" s="69" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+      <c r="E25" s="69"/>
+      <c r="F25" s="70" t="s">
         <v>190</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="68" t="s">
         <v>191</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="C26" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="69" t="s">
         <v>192</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
+      <c r="E26" s="69"/>
+      <c r="F26" s="70" t="s">
         <v>193</v>
       </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="69" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" s="69"/>
+      <c r="F27" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="69" t="s">
+        <v>198</v>
+      </c>
+      <c r="E28" s="69"/>
+      <c r="F28" s="70" t="s">
+        <v>199</v>
+      </c>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="69"/>
+      <c r="F29" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="70" t="s">
-        <v>194</v>
+      <c r="B30" s="68" t="s">
+        <v>203</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="E30" s="71"/>
-      <c r="F30" s="72" t="s">
-        <v>197</v>
-      </c>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="70" t="s">
-        <v>198</v>
-      </c>
-      <c r="C31" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="D31" s="71" t="s">
-        <v>199</v>
-      </c>
-      <c r="E31" s="71"/>
-      <c r="F31" s="72" t="s">
-        <v>200</v>
-      </c>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="70" t="s">
-        <v>201</v>
-      </c>
-      <c r="C32" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="D32" s="71" t="s">
-        <v>202</v>
-      </c>
-      <c r="E32" s="71"/>
-      <c r="F32" s="72" t="s">
-        <v>203</v>
-      </c>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="70" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="C33" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="D33" s="71" t="s">
+      <c r="E30" s="69"/>
+      <c r="F30" s="70" t="s">
         <v>205</v>
       </c>
-      <c r="E33" s="71"/>
-      <c r="F33" s="72" t="s">
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="58" t="s">
         <v>206</v>
       </c>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="70" t="s">
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="71" t="s">
         <v>207</v>
       </c>
-      <c r="C34" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="D34" s="71" t="s">
-        <v>208</v>
-      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
       <c r="E34" s="71"/>
-      <c r="F34" s="72" t="s">
-        <v>209</v>
-      </c>
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="70" t="s">
-        <v>210</v>
-      </c>
-      <c r="C35" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" s="71" t="s">
-        <v>211</v>
-      </c>
-      <c r="E35" s="71"/>
-      <c r="F35" s="72" t="s">
-        <v>212</v>
-      </c>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="58" t="s">
-        <v>213</v>
-      </c>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="73" t="s">
-        <v>214</v>
-      </c>
-      <c r="C39" s="73"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="B34:H34"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4687,37 +4554,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="215">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -546,6 +546,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -586,6 +601,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -915,7 +936,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -999,6 +1020,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3933,7 +3960,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4182,333 +4209,439 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="60">
-        <v>0.32097512437810943</v>
-      </c>
-      <c r="D16" s="60">
-        <v>0.2631922899201267</v>
-      </c>
-      <c r="E16" s="60">
-        <v>0.19337932333482447</v>
-      </c>
-      <c r="F16" s="60">
-        <v>0.16157607242446237</v>
-      </c>
-      <c r="G16" s="60">
-        <v>0.1456539181599358</v>
-      </c>
-      <c r="H16" s="62" t="s">
+      <c r="C16" s="63">
+        <v>6671.066666666667</v>
+      </c>
+      <c r="D16" s="63">
+        <v>5501.590909090909</v>
+      </c>
+      <c r="E16" s="63">
+        <v>4337.833333333333</v>
+      </c>
+      <c r="F16" s="63">
+        <v>3841.1111111111113</v>
+      </c>
+      <c r="G16" s="63">
+        <v>3633.175</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="58" t="s">
+      <c r="C17" s="57">
+        <v>400</v>
+      </c>
+      <c r="D17" s="57">
+        <v>412</v>
+      </c>
+      <c r="E17" s="57">
+        <v>424</v>
+      </c>
+      <c r="F17" s="57">
+        <v>437</v>
+      </c>
+      <c r="G17" s="57">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C17" s="60">
-        <v>0.12835820895522387</v>
-      </c>
-      <c r="D17" s="60">
-        <v>0.08763944814839263</v>
-      </c>
-      <c r="E17" s="60">
-        <v>0.06433837967650036</v>
-      </c>
-      <c r="F17" s="60">
-        <v>0.05370889491577219</v>
-      </c>
-      <c r="G17" s="60">
-        <v>0.048391933498261576</v>
-      </c>
-      <c r="H17" s="62" t="s">
+      <c r="C18" s="61">
+        <v>1720</v>
+      </c>
+      <c r="D18" s="61">
+        <v>1206.9545454545455</v>
+      </c>
+      <c r="E18" s="61">
+        <v>910.8813333333333</v>
+      </c>
+      <c r="F18" s="61">
+        <v>781.1362</v>
+      </c>
+      <c r="G18" s="61">
+        <v>723.7497574000001</v>
+      </c>
+      <c r="H18" s="62" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="58" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="C18" s="60">
-        <v>0.5021592039800995</v>
-      </c>
-      <c r="D18" s="60">
-        <v>0.6005181860188792</v>
-      </c>
-      <c r="E18" s="60">
-        <v>0.6936053492807195</v>
-      </c>
-      <c r="F18" s="60">
-        <v>0.7358951831620765</v>
-      </c>
-      <c r="G18" s="60">
-        <v>0.7570757555496122</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="58" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" s="63">
-        <v>3</v>
-      </c>
-      <c r="D19" s="63">
-        <v>3</v>
-      </c>
-      <c r="E19" s="63">
-        <v>3</v>
-      </c>
-      <c r="F19" s="63">
-        <v>3</v>
-      </c>
-      <c r="G19" s="63">
-        <v>3</v>
-      </c>
-      <c r="H19" s="62" t="s">
-        <v>176</v>
+      <c r="C19" s="64">
+        <v>6728.933333333333</v>
+      </c>
+      <c r="D19" s="64">
+        <v>8270.227272727272</v>
+      </c>
+      <c r="E19" s="64">
+        <v>9819.833333333334</v>
+      </c>
+      <c r="F19" s="64">
+        <v>10702.777777777777</v>
+      </c>
+      <c r="G19" s="64">
+        <v>11322.825</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="D20" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="E20" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="F20" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="G20" s="64" t="s">
-        <v>178</v>
+        <v>174</v>
+      </c>
+      <c r="C20" s="60">
+        <v>0.32097512437810943</v>
+      </c>
+      <c r="D20" s="60">
+        <v>0.2631922899201267</v>
+      </c>
+      <c r="E20" s="60">
+        <v>0.19337932333482447</v>
+      </c>
+      <c r="F20" s="60">
+        <v>0.16157607242446237</v>
+      </c>
+      <c r="G20" s="60">
+        <v>0.1456539181599358</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="60">
+        <v>0.12835820895522387</v>
+      </c>
+      <c r="D21" s="60">
+        <v>0.08763944814839263</v>
+      </c>
+      <c r="E21" s="60">
+        <v>0.06433837967650036</v>
+      </c>
+      <c r="F21" s="60">
+        <v>0.05370889491577219</v>
+      </c>
+      <c r="G21" s="60">
+        <v>0.048391933498261576</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="58" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="60">
+        <v>0.5021592039800995</v>
+      </c>
+      <c r="D22" s="60">
+        <v>0.6005181860188792</v>
+      </c>
+      <c r="E22" s="60">
+        <v>0.6936053492807195</v>
+      </c>
+      <c r="F22" s="60">
+        <v>0.7358951831620765</v>
+      </c>
+      <c r="G22" s="60">
+        <v>0.7570757555496122</v>
+      </c>
+      <c r="H22" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="C21" s="45" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" s="65">
+        <v>3</v>
+      </c>
+      <c r="D23" s="65">
+        <v>3</v>
+      </c>
+      <c r="E23" s="65">
+        <v>3</v>
+      </c>
+      <c r="F23" s="65">
+        <v>3</v>
+      </c>
+      <c r="G23" s="65">
+        <v>3</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="C24" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="D24" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="F24" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="G24" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="C25" s="45" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="65" t="str">
+      <c r="D25" s="67" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="65" t="str">
+      <c r="E25" s="67" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="65" t="str">
+      <c r="F25" s="67" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="65" t="str">
+      <c r="G25" s="67" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="62" t="s">
+      <c r="H25" s="62" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="C22" s="66">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="68">
         <v>12</v>
       </c>
-      <c r="D22" s="63">
+      <c r="D26" s="65">
         <v>28</v>
       </c>
-      <c r="E22" s="63">
+      <c r="E26" s="65">
         <v>53</v>
       </c>
-      <c r="F22" s="67" t="s">
-        <v>181</v>
-      </c>
-      <c r="G22" s="67" t="s">
-        <v>181</v>
-      </c>
-      <c r="H22" s="62" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
+      <c r="F26" s="69" t="s">
         <v>186</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="68" t="s">
+      <c r="G26" s="69" t="s">
+        <v>186</v>
+      </c>
+      <c r="H26" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="C25" s="45" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="69" t="s">
+      <c r="C27" s="65">
+        <v>368</v>
+      </c>
+      <c r="D27" s="65">
+        <v>853</v>
+      </c>
+      <c r="E27" s="65">
+        <v>1620</v>
+      </c>
+      <c r="F27" s="65">
+        <v>2541</v>
+      </c>
+      <c r="G27" s="65">
+        <v>3556</v>
+      </c>
+      <c r="H27" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="E25" s="69"/>
-      <c r="F25" s="70" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="68" t="s">
+      <c r="C29" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C26" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="D26" s="69" t="s">
+      <c r="D29" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E26" s="69"/>
-      <c r="F26" s="70" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="68" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="70" t="s">
         <v>194</v>
       </c>
-      <c r="C27" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="D27" s="69" t="s">
+      <c r="C30" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="E27" s="69"/>
-      <c r="F27" s="70" t="s">
+      <c r="D30" s="71" t="s">
         <v>196</v>
       </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="68" t="s">
+      <c r="E30" s="71"/>
+      <c r="F30" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="C28" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="D28" s="69" t="s">
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="70" t="s">
         <v>198</v>
       </c>
-      <c r="E28" s="69"/>
-      <c r="F28" s="70" t="s">
+      <c r="C31" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="71" t="s">
         <v>199</v>
       </c>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="68" t="s">
+      <c r="E31" s="71"/>
+      <c r="F31" s="72" t="s">
         <v>200</v>
       </c>
-      <c r="C29" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="D29" s="69" t="s">
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="70" t="s">
         <v>201</v>
       </c>
-      <c r="E29" s="69"/>
-      <c r="F29" s="70" t="s">
+      <c r="C32" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D32" s="71" t="s">
         <v>202</v>
       </c>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="68" t="s">
+      <c r="E32" s="71"/>
+      <c r="F32" s="72" t="s">
         <v>203</v>
       </c>
-      <c r="C30" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="D30" s="69" t="s">
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="70" t="s">
         <v>204</v>
       </c>
-      <c r="E30" s="69"/>
-      <c r="F30" s="70" t="s">
+      <c r="C33" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33" s="71" t="s">
         <v>205</v>
       </c>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="68" t="s">
+      <c r="E33" s="71"/>
+      <c r="F33" s="72" t="s">
+        <v>206</v>
+      </c>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="70" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34" s="71" t="s">
+        <v>208</v>
+      </c>
+      <c r="E34" s="71"/>
+      <c r="F34" s="72" t="s">
+        <v>209</v>
+      </c>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="70" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="E35" s="71"/>
+      <c r="F35" s="72" t="s">
+        <v>212</v>
+      </c>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="58" t="s">
-        <v>206</v>
-      </c>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="71" t="s">
-        <v>207</v>
-      </c>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="C37" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="73" t="s">
+        <v>214</v>
+      </c>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4554,37 +4687,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -15,19 +15,19 @@
     <sheet sheetId="9" name="Financial Health" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$F40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$F41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staffing &amp; Personnel'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Operating Expenses'!$A1:$F15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Operating Expenses'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Capital &amp; Debt'!$A1:$F4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="219">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -168,6 +168,9 @@
     <t>July</t>
   </si>
   <si>
+    <t>Accounting Basis</t>
+  </si>
+  <si>
     <t>Year 1 Operating Months</t>
   </si>
   <si>
@@ -423,6 +426,15 @@
     <t>Total OCCUPANCY</t>
   </si>
   <si>
+    <t>ADMINISTRATIVE / GENERAL</t>
+  </si>
+  <si>
+    <t>Compliance Contract</t>
+  </si>
+  <si>
+    <t>Total ADMINISTRATIVE</t>
+  </si>
+  <si>
     <t>TOTAL OPERATING EXPENSES</t>
   </si>
   <si>
@@ -504,7 +516,7 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -672,7 +684,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>116.9 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>111.6 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -863,7 +875,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E1"/>
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1541,7 +1553,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1659,70 +1671,70 @@
       <c r="A14" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="23">
-        <v>10</v>
+      <c r="B14" s="23" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>45</v>
+      <c r="B15" s="23">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>46</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="23" t="s">
         <v>50</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="23" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="B20" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="8"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="24">
-        <v>15</v>
-      </c>
+      <c r="B22" s="8"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>56</v>
       </c>
       <c r="B23" s="24">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1730,7 +1742,7 @@
         <v>57</v>
       </c>
       <c r="B24" s="24">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1738,7 +1750,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="24">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1746,57 +1758,45 @@
         <v>59</v>
       </c>
       <c r="B26" s="24">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="24">
         <v>40</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="25" t="s">
+    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="E29" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="F29" s="25" t="s">
-        <v>65</v>
-      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" s="25" t="s">
         <v>66</v>
-      </c>
-      <c r="B30" s="26">
-        <v>3</v>
-      </c>
-      <c r="C30" s="26">
-        <v>4</v>
-      </c>
-      <c r="D30" s="26">
-        <v>5</v>
-      </c>
-      <c r="E30" s="26">
-        <v>6</v>
-      </c>
-      <c r="F30" s="26">
-        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1804,19 +1804,19 @@
         <v>67</v>
       </c>
       <c r="B31" s="26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" s="26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1824,107 +1824,127 @@
         <v>68</v>
       </c>
       <c r="B32" s="26">
+        <v>2</v>
+      </c>
+      <c r="C32" s="26">
+        <v>3</v>
+      </c>
+      <c r="D32" s="26">
+        <v>4</v>
+      </c>
+      <c r="E32" s="26">
         <v>5</v>
       </c>
-      <c r="C32" s="26">
+      <c r="F32" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" s="26">
+        <v>5</v>
+      </c>
+      <c r="C33" s="26">
         <v>7</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D33" s="26">
         <v>9</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E33" s="26">
         <v>10</v>
       </c>
-      <c r="F32" s="26">
+      <c r="F33" s="26">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33" s="28">
-        <f>B30+B31+B32</f>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="28">
+        <f>B31+B32+B33</f>
         <v>10</v>
       </c>
-      <c r="C33" s="28">
-        <f>C30+C31+C32</f>
+      <c r="C34" s="28">
+        <f>C31+C32+C33</f>
         <v>14</v>
       </c>
-      <c r="D33" s="28">
-        <f>D30+D31+D32</f>
+      <c r="D34" s="28">
+        <f>D31+D32+D33</f>
         <v>18</v>
       </c>
-      <c r="E33" s="28">
-        <f>E30+E31+E32</f>
+      <c r="E34" s="28">
+        <f>E31+E32+E33</f>
         <v>21</v>
       </c>
-      <c r="F33" s="28">
-        <f>F30+F31+F32</f>
+      <c r="F34" s="28">
+        <f>F31+F32+F33</f>
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="B34" s="30">
-        <f>IF(B22=0,0,B33/B22)</f>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" s="30">
+        <f>IF(B23=0,0,B34/B23)</f>
         <v>0.66666667</v>
       </c>
-      <c r="C34" s="30">
-        <f>IF(C23=0,0,C33/C23)</f>
+      <c r="C35" s="30">
+        <f>IF(C24=0,0,C34/C24)</f>
         <v>0.63636364</v>
       </c>
-      <c r="D34" s="30">
-        <f>IF(D24=0,0,D33/D24)</f>
+      <c r="D35" s="30">
+        <f>IF(D25=0,0,D34/D25)</f>
         <v>0.6</v>
       </c>
-      <c r="E34" s="30">
-        <f>IF(E25=0,0,E33/E25)</f>
+      <c r="E35" s="30">
+        <f>IF(E26=0,0,E34/E26)</f>
         <v>0.58333333</v>
       </c>
-      <c r="F34" s="30">
-        <f>IF(F26=0,0,F33/F26)</f>
+      <c r="F35" s="30">
+        <f>IF(F27=0,0,F34/F27)</f>
         <v>0.575</v>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="8"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
+    <row r="37" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="31">
-        <v>0.03</v>
-      </c>
+      <c r="B37" s="8"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
         <v>73</v>
       </c>
       <c r="B38" s="31">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="32">
-        <v>0.8333333333333334</v>
+      <c r="B39" s="31">
+        <v>0.025</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="33" t="s">
+      <c r="B40" s="32">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="22" t="s">
         <v>76</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1957,49 +1977,49 @@
         <v>23</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B2" s="35">
-        <f>Assumptions!B22</f>
+        <f>Assumptions!B23</f>
         <v>15</v>
       </c>
       <c r="C2" s="35">
-        <f>Assumptions!B23</f>
+        <f>Assumptions!B24</f>
         <v>22</v>
       </c>
       <c r="D2" s="35">
-        <f>Assumptions!B24</f>
+        <f>Assumptions!B25</f>
         <v>30</v>
       </c>
       <c r="E2" s="35">
-        <f>Assumptions!B25</f>
+        <f>Assumptions!B26</f>
         <v>36</v>
       </c>
       <c r="F2" s="35">
-        <f>Assumptions!B26</f>
+        <f>Assumptions!B27</f>
         <v>40</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2009,57 +2029,57 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="36">
-        <f>6000*Assumptions!B22</f>
+        <f>6000*Assumptions!B23</f>
         <v>90000</v>
       </c>
       <c r="C4" s="36">
-        <f>6180*Assumptions!B23</f>
+        <f>6180*Assumptions!B24</f>
         <v>135960</v>
       </c>
       <c r="D4" s="36">
-        <f>6365*Assumptions!B24</f>
+        <f>6365*Assumptions!B25</f>
         <v>190950</v>
       </c>
       <c r="E4" s="36">
-        <f>6556*Assumptions!B25</f>
+        <f>6556*Assumptions!B26</f>
         <v>236016</v>
       </c>
       <c r="F4" s="36">
-        <f>6753*Assumptions!B26</f>
+        <f>6753*Assumptions!B27</f>
         <v>270120</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5" s="36">
-        <f>200*Assumptions!B22</f>
+        <f>200*Assumptions!B23</f>
         <v>3000</v>
       </c>
       <c r="C5" s="36">
-        <f>200*Assumptions!B23</f>
+        <f>200*Assumptions!B24</f>
         <v>4400</v>
       </c>
       <c r="D5" s="36">
-        <f>200*Assumptions!B24</f>
+        <f>200*Assumptions!B25</f>
         <v>6000</v>
       </c>
       <c r="E5" s="36">
-        <f>200*Assumptions!B25</f>
+        <f>200*Assumptions!B26</f>
         <v>7200</v>
       </c>
       <c r="F5" s="36">
-        <f>200*Assumptions!B26</f>
+        <f>200*Assumptions!B27</f>
         <v>8000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" s="37">
         <f>SUM(B4:B5)</f>
@@ -2084,7 +2104,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2094,32 +2114,32 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B8" s="36">
-        <f>7000*Assumptions!B22</f>
+        <f>7000*Assumptions!B23</f>
         <v>105000</v>
       </c>
       <c r="C8" s="36">
-        <f>7210*Assumptions!B23</f>
+        <f>7210*Assumptions!B24</f>
         <v>158620</v>
       </c>
       <c r="D8" s="36">
-        <f>7426*Assumptions!B24</f>
+        <f>7426*Assumptions!B25</f>
         <v>222780</v>
       </c>
       <c r="E8" s="36">
-        <f>7649*Assumptions!B25</f>
+        <f>7649*Assumptions!B26</f>
         <v>275364</v>
       </c>
       <c r="F8" s="36">
-        <f>7878*Assumptions!B26</f>
+        <f>7878*Assumptions!B27</f>
         <v>315120</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="37">
         <f>SUM(B8:B8)</f>
@@ -2144,7 +2164,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2154,7 +2174,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="36">
         <v>3000</v>
@@ -2174,7 +2194,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" s="37">
         <f>SUM(B11:B11)</f>
@@ -2199,7 +2219,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" s="37">
         <f>B6+B9+B12</f>
@@ -2246,7 +2266,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -2258,39 +2278,39 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D4" s="32">
         <v>1</v>
@@ -2310,13 +2330,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" s="32">
         <v>0.5</v>
@@ -2336,7 +2356,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2348,7 +2368,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" s="27">
         <v>2</v>
@@ -2356,7 +2376,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B9" s="27">
         <v>1.5</v>
@@ -2364,7 +2384,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B10" s="40">
         <v>63000</v>
@@ -2372,7 +2392,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" s="40">
         <v>9600</v>
@@ -2380,7 +2400,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B12" s="40">
         <v>4820</v>
@@ -2388,7 +2408,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B13" s="40">
         <v>0</v>
@@ -2396,7 +2416,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="41">
         <v>77420</v>
@@ -2404,7 +2424,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -2417,24 +2437,24 @@
         <v>23</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B18" s="36">
         <v>77420</v>
@@ -2454,35 +2474,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B19" s="42">
-        <f>(1+Assumptions!B37)^0</f>
+        <f>(1+Assumptions!B38)^0</f>
         <v>1</v>
       </c>
       <c r="C19" s="42">
-        <f>(1+Assumptions!B37)^1</f>
+        <f>(1+Assumptions!B38)^1</f>
         <v>1.03</v>
       </c>
       <c r="D19" s="42">
-        <f>(1+Assumptions!B37)^2</f>
+        <f>(1+Assumptions!B38)^2</f>
         <v>1.0609</v>
       </c>
       <c r="E19" s="42">
-        <f>(1+Assumptions!B37)^3</f>
+        <f>(1+Assumptions!B38)^3</f>
         <v>1.092727</v>
       </c>
       <c r="F19" s="42">
-        <f>(1+Assumptions!B37)^4</f>
+        <f>(1+Assumptions!B38)^4</f>
         <v>1.1255088100000001</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" s="43">
-        <f>Assumptions!B39</f>
+        <f>Assumptions!B40</f>
         <v>0.8333333333333334</v>
       </c>
       <c r="C20" s="43">
@@ -2500,7 +2520,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B21" s="37">
         <f>B18*B19*B20</f>
@@ -2541,7 +2561,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -2553,49 +2573,49 @@
         <v>23</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B2" s="35">
-        <f>Assumptions!B22</f>
+        <f>Assumptions!B23</f>
         <v>15</v>
       </c>
       <c r="C2" s="35">
-        <f>Assumptions!B23</f>
+        <f>Assumptions!B24</f>
         <v>22</v>
       </c>
       <c r="D2" s="35">
-        <f>Assumptions!B24</f>
+        <f>Assumptions!B25</f>
         <v>30</v>
       </c>
       <c r="E2" s="35">
-        <f>Assumptions!B25</f>
+        <f>Assumptions!B26</f>
         <v>36</v>
       </c>
       <c r="F2" s="35">
-        <f>Assumptions!B26</f>
+        <f>Assumptions!B27</f>
         <v>40</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2605,32 +2625,32 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B4" s="36">
-        <f>400*Assumptions!B22</f>
+        <f>400*Assumptions!B23</f>
         <v>6000</v>
       </c>
       <c r="C4" s="36">
-        <f>412*Assumptions!B23</f>
+        <f>412*Assumptions!B24</f>
         <v>9064</v>
       </c>
       <c r="D4" s="36">
-        <f>424*Assumptions!B24</f>
+        <f>424*Assumptions!B25</f>
         <v>12720</v>
       </c>
       <c r="E4" s="36">
-        <f>437*Assumptions!B25</f>
+        <f>437*Assumptions!B26</f>
         <v>15732</v>
       </c>
       <c r="F4" s="36">
-        <f>450*Assumptions!B26</f>
+        <f>450*Assumptions!B27</f>
         <v>18000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B5" s="37">
         <f>SUM(B4:B4)</f>
@@ -2655,7 +2675,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2665,32 +2685,32 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B7" s="36">
-        <f>250*Assumptions!B22</f>
+        <f>250*Assumptions!B23</f>
         <v>3750</v>
       </c>
       <c r="C7" s="36">
-        <f>258*Assumptions!B23</f>
+        <f>258*Assumptions!B24</f>
         <v>5676</v>
       </c>
       <c r="D7" s="36">
-        <f>265*Assumptions!B24</f>
+        <f>265*Assumptions!B25</f>
         <v>7950</v>
       </c>
       <c r="E7" s="36">
-        <f>273*Assumptions!B25</f>
+        <f>273*Assumptions!B26</f>
         <v>9828</v>
       </c>
       <c r="F7" s="36">
-        <f>281*Assumptions!B26</f>
+        <f>281*Assumptions!B27</f>
         <v>11240</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" s="37">
         <f>SUM(B7:B7)</f>
@@ -2715,7 +2735,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2725,7 +2745,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" s="36">
         <f>1800*12</f>
@@ -2750,7 +2770,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B11" s="36">
         <f>200*12</f>
@@ -2775,7 +2795,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B12" s="36">
         <v>1800</v>
@@ -2795,7 +2815,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B13" s="37">
         <f>SUM(B10:B12)</f>
@@ -2818,29 +2838,84 @@
         <v>28951</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B15" s="37">
-        <f>B5+B8+B13</f>
-        <v>35550</v>
-      </c>
-      <c r="C15" s="37">
-        <f>C5+C8+C13</f>
-        <v>41293</v>
-      </c>
-      <c r="D15" s="37">
-        <f>D5+D8+D13</f>
-        <v>48001</v>
-      </c>
-      <c r="E15" s="37">
-        <f>E5+E8+E13</f>
-        <v>53682</v>
-      </c>
-      <c r="F15" s="37">
-        <f>F5+F8+F13</f>
-        <v>58191</v>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="36">
+        <v>4500</v>
+      </c>
+      <c r="C15" s="36">
+        <v>4500</v>
+      </c>
+      <c r="D15" s="36">
+        <v>4500</v>
+      </c>
+      <c r="E15" s="36">
+        <v>4500</v>
+      </c>
+      <c r="F15" s="36">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="37">
+        <f>SUM(B15:B15)</f>
+        <v>4500</v>
+      </c>
+      <c r="C16" s="37">
+        <f>SUM(C15:C15)</f>
+        <v>4500</v>
+      </c>
+      <c r="D16" s="37">
+        <f>SUM(D15:D15)</f>
+        <v>4500</v>
+      </c>
+      <c r="E16" s="37">
+        <f>SUM(E15:E15)</f>
+        <v>4500</v>
+      </c>
+      <c r="F16" s="37">
+        <f>SUM(F15:F15)</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="37">
+        <f>B5+B8+B13+B16</f>
+        <v>40050</v>
+      </c>
+      <c r="C18" s="37">
+        <f>C5+C8+C13+C16</f>
+        <v>45793</v>
+      </c>
+      <c r="D18" s="37">
+        <f>D5+D8+D13+D16</f>
+        <v>52501</v>
+      </c>
+      <c r="E18" s="37">
+        <f>E5+E8+E13+E16</f>
+        <v>58182</v>
+      </c>
+      <c r="F18" s="37">
+        <f>F5+F8+F13+F16</f>
+        <v>62691</v>
       </c>
     </row>
   </sheetData>
@@ -2870,24 +2945,24 @@
         <v>23</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2897,7 +2972,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B3" s="36">
         <v>0</v>
@@ -2917,7 +2992,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B4" s="37">
         <v>0</v>
@@ -2962,24 +3037,24 @@
         <v>1</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B2" s="36">
         <f>'Revenue Schedule'!B14</f>
@@ -3004,7 +3079,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B3" s="36">
         <f>'Staffing &amp; Personnel'!B21</f>
@@ -3032,24 +3107,24 @@
         <v>17</v>
       </c>
       <c r="B4" s="36">
-        <f>'Operating Expenses'!B15</f>
-        <v>35550</v>
+        <f>'Operating Expenses'!B18</f>
+        <v>40050</v>
       </c>
       <c r="C4" s="36">
-        <f>'Operating Expenses'!C15</f>
-        <v>41293</v>
+        <f>'Operating Expenses'!C18</f>
+        <v>45793</v>
       </c>
       <c r="D4" s="36">
-        <f>'Operating Expenses'!D15</f>
-        <v>48001</v>
+        <f>'Operating Expenses'!D18</f>
+        <v>52501</v>
       </c>
       <c r="E4" s="36">
-        <f>'Operating Expenses'!E15</f>
-        <v>53682</v>
+        <f>'Operating Expenses'!E18</f>
+        <v>58182</v>
       </c>
       <c r="F4" s="36">
-        <f>'Operating Expenses'!F15</f>
-        <v>58191</v>
+        <f>'Operating Expenses'!F18</f>
+        <v>62691</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3079,77 +3154,77 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B6" s="37">
         <f>B3+B4+B5</f>
-        <v>100066</v>
+        <v>104566</v>
       </c>
       <c r="C6" s="37">
         <f>C3+C4+C5</f>
-        <v>121035</v>
+        <v>125535</v>
       </c>
       <c r="D6" s="37">
         <f>D3+D4+D5</f>
-        <v>130135</v>
+        <v>134635</v>
       </c>
       <c r="E6" s="37">
         <f>E3+E4+E5</f>
-        <v>138280</v>
+        <v>142780</v>
       </c>
       <c r="F6" s="37">
         <f>F3+F4+F5</f>
-        <v>145327</v>
+        <v>149827</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B7" s="37">
         <f>B2-B6</f>
-        <v>100934</v>
+        <v>96434</v>
       </c>
       <c r="C7" s="37">
         <f>C2-C6</f>
-        <v>181945</v>
+        <v>177445</v>
       </c>
       <c r="D7" s="37">
         <f>D2-D6</f>
-        <v>294595</v>
+        <v>290095</v>
       </c>
       <c r="E7" s="37">
         <f>E2-E6</f>
-        <v>385300</v>
+        <v>380800</v>
       </c>
       <c r="F7" s="37">
         <f>F2-F6</f>
-        <v>452913</v>
+        <v>448413</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B8" s="36">
         <f>B7</f>
-        <v>100934</v>
+        <v>96434</v>
       </c>
       <c r="C8" s="36">
         <f>B8+C7</f>
-        <v>282879</v>
+        <v>273879</v>
       </c>
       <c r="D8" s="36">
         <f>C8+D7</f>
-        <v>577474</v>
+        <v>563974</v>
       </c>
       <c r="E8" s="36">
         <f>D8+E7</f>
-        <v>962774</v>
+        <v>944774</v>
       </c>
       <c r="F8" s="36">
         <f>E8+F7</f>
-        <v>1415687</v>
+        <v>1393187</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3158,31 +3233,31 @@
       </c>
       <c r="B9" s="44">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
-        <v>12.10409129974217</v>
+        <v>11.066771225828662</v>
       </c>
       <c r="C9" s="44">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
-        <v>28.04600322220845</v>
+        <v>26.180332178276974</v>
       </c>
       <c r="D9" s="44">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
-        <v>53.249994236754134</v>
+        <v>50.26692910461618</v>
       </c>
       <c r="E9" s="44">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
-        <v>83.54995660977725</v>
+        <v>79.40389410281551</v>
       </c>
       <c r="F9" s="44">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
-        <v>116.8966812773951</v>
+        <v>111.5836531466291</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C10" s="46" t="s">
         <v>23</v>
@@ -3212,7 +3287,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -3221,7 +3296,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -3231,7 +3306,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3302,463 +3377,471 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="B13" s="27" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="34" t="s">
+      <c r="B16" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="C16" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="D16" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="34" t="s">
+      <c r="E16" s="34" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="35">
+      <c r="F16" s="34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="35">
         <f>'Revenue Schedule'!B2</f>
         <v>15</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C17" s="35">
         <f>'Revenue Schedule'!C2</f>
         <v>22</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D17" s="35">
         <f>'Revenue Schedule'!D2</f>
         <v>30</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E17" s="35">
         <f>'Revenue Schedule'!E2</f>
         <v>36</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F17" s="35">
         <f>'Revenue Schedule'!F2</f>
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C17" s="49">
-        <f>IF(B16=0,0,(C16-B16)/B16)</f>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="49">
+        <f>IF(B17=0,0,(C17-B17)/B17)</f>
         <v>0.4666666666666667</v>
       </c>
-      <c r="D17" s="49">
-        <f>IF(C16=0,0,(D16-C16)/C16)</f>
+      <c r="D18" s="49">
+        <f>IF(C17=0,0,(D17-C17)/C17)</f>
         <v>0.36363636363636365</v>
       </c>
-      <c r="E17" s="49">
-        <f>IF(D16=0,0,(E16-D16)/D16)</f>
+      <c r="E18" s="49">
+        <f>IF(D17=0,0,(E17-D17)/D17)</f>
         <v>0.2</v>
       </c>
-      <c r="F17" s="49">
-        <f>IF(E16=0,0,(F16-E16)/E16)</f>
+      <c r="F18" s="49">
+        <f>IF(E17=0,0,(F17-E17)/E17)</f>
         <v>0.1111111111111111</v>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="34" t="s">
+      <c r="B20" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="C20" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="D20" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="34" t="s">
+      <c r="E20" s="34" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="36">
+      <c r="F20" s="34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="36">
         <f>'Financial Model'!B2</f>
         <v>201000</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C21" s="36">
         <f>'Financial Model'!C2</f>
         <v>302980</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D21" s="36">
         <f>'Financial Model'!D2</f>
         <v>424730</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E21" s="36">
         <f>'Financial Model'!E2</f>
         <v>523580</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F21" s="36">
         <f>'Financial Model'!F2</f>
         <v>598240</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="B21" s="36">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="36">
         <f>'Financial Model'!B3</f>
         <v>64516</v>
       </c>
-      <c r="C21" s="36">
+      <c r="C22" s="36">
         <f>'Financial Model'!C3</f>
         <v>79742</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D22" s="36">
         <f>'Financial Model'!D3</f>
         <v>82134</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E22" s="36">
         <f>'Financial Model'!E3</f>
         <v>84598</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F22" s="36">
         <f>'Financial Model'!F3</f>
         <v>87136</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="36">
+      <c r="B23" s="36">
         <f>'Financial Model'!B4</f>
-        <v>35550</v>
-      </c>
-      <c r="C22" s="36">
+        <v>40050</v>
+      </c>
+      <c r="C23" s="36">
         <f>'Financial Model'!C4</f>
-        <v>41293</v>
-      </c>
-      <c r="D22" s="36">
+        <v>45793</v>
+      </c>
+      <c r="D23" s="36">
         <f>'Financial Model'!D4</f>
-        <v>48001</v>
-      </c>
-      <c r="E22" s="36">
+        <v>52501</v>
+      </c>
+      <c r="E23" s="36">
         <f>'Financial Model'!E4</f>
-        <v>53682</v>
-      </c>
-      <c r="F22" s="36">
+        <v>58182</v>
+      </c>
+      <c r="F23" s="36">
         <f>'Financial Model'!F4</f>
-        <v>58191</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B23" s="37">
+        <v>62691</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="37">
         <f>'Financial Model'!B6</f>
-        <v>100066</v>
-      </c>
-      <c r="C23" s="37">
+        <v>104566</v>
+      </c>
+      <c r="C24" s="37">
         <f>'Financial Model'!C6</f>
-        <v>121035</v>
-      </c>
-      <c r="D23" s="37">
+        <v>125535</v>
+      </c>
+      <c r="D24" s="37">
         <f>'Financial Model'!D6</f>
-        <v>130135</v>
-      </c>
-      <c r="E23" s="37">
+        <v>134635</v>
+      </c>
+      <c r="E24" s="37">
         <f>'Financial Model'!E6</f>
-        <v>138280</v>
-      </c>
-      <c r="F23" s="37">
+        <v>142780</v>
+      </c>
+      <c r="F24" s="37">
         <f>'Financial Model'!F6</f>
-        <v>145327</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="B24" s="50">
+        <v>149827</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B25" s="50">
         <f>'Financial Model'!B7</f>
-        <v>100934</v>
-      </c>
-      <c r="C24" s="50">
+        <v>96434</v>
+      </c>
+      <c r="C25" s="50">
         <f>'Financial Model'!C7</f>
-        <v>181945</v>
-      </c>
-      <c r="D24" s="50">
+        <v>177445</v>
+      </c>
+      <c r="D25" s="50">
         <f>'Financial Model'!D7</f>
-        <v>294595</v>
-      </c>
-      <c r="E24" s="50">
+        <v>290095</v>
+      </c>
+      <c r="E25" s="50">
         <f>'Financial Model'!E7</f>
-        <v>385300</v>
-      </c>
-      <c r="F24" s="50">
+        <v>380800</v>
+      </c>
+      <c r="F25" s="50">
         <f>'Financial Model'!F7</f>
-        <v>452913</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="B25" s="36">
+        <v>448413</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="36">
         <f>'Financial Model'!B8</f>
-        <v>100934</v>
-      </c>
-      <c r="C25" s="36">
+        <v>96434</v>
+      </c>
+      <c r="C26" s="36">
         <f>'Financial Model'!C8</f>
-        <v>282879</v>
-      </c>
-      <c r="D25" s="36">
+        <v>273879</v>
+      </c>
+      <c r="D26" s="36">
         <f>'Financial Model'!D8</f>
-        <v>577474</v>
-      </c>
-      <c r="E25" s="36">
+        <v>563974</v>
+      </c>
+      <c r="E26" s="36">
         <f>'Financial Model'!E8</f>
-        <v>962774</v>
-      </c>
-      <c r="F25" s="36">
+        <v>944774</v>
+      </c>
+      <c r="F26" s="36">
         <f>'Financial Model'!F8</f>
-        <v>1415687</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
+        <v>1393187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B27" s="13">
         <f>'Financial Model'!B9</f>
-        <v>12.10409129974217</v>
-      </c>
-      <c r="C26" s="13">
+        <v>11.066771225828662</v>
+      </c>
+      <c r="C27" s="13">
         <f>'Financial Model'!C9</f>
-        <v>28.04600322220845</v>
-      </c>
-      <c r="D26" s="13">
+        <v>26.180332178276974</v>
+      </c>
+      <c r="D27" s="13">
         <f>'Financial Model'!D9</f>
-        <v>53.249994236754134</v>
-      </c>
-      <c r="E26" s="13">
+        <v>50.26692910461618</v>
+      </c>
+      <c r="E27" s="13">
         <f>'Financial Model'!E9</f>
-        <v>83.54995660977725</v>
-      </c>
-      <c r="F26" s="13">
+        <v>79.40389410281551</v>
+      </c>
+      <c r="F27" s="13">
         <f>'Financial Model'!F9</f>
-        <v>116.8966812773951</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="B29" s="36">
-        <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
-        <v>13400</v>
-      </c>
-      <c r="C29" s="36">
-        <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
-        <v>13771.818181818182</v>
-      </c>
-      <c r="D29" s="36">
-        <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
-        <v>14157.666666666666</v>
-      </c>
-      <c r="E29" s="36">
-        <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
-        <v>14543.888888888889</v>
-      </c>
-      <c r="F29" s="36">
-        <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
-        <v>14956</v>
-      </c>
+        <v>111.5836531466291</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="B30" s="49">
-        <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
-        <v>0.32097512437810943</v>
-      </c>
-      <c r="C30" s="49">
-        <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
-        <v>0.2631922899201267</v>
-      </c>
-      <c r="D30" s="49">
-        <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
-        <v>0.19337932333482447</v>
-      </c>
-      <c r="E30" s="49">
-        <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
-        <v>0.16157607242446237</v>
-      </c>
-      <c r="F30" s="49">
-        <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
-        <v>0.1456539181599358</v>
+        <v>150</v>
+      </c>
+      <c r="B30" s="36">
+        <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
+        <v>13400</v>
+      </c>
+      <c r="C30" s="36">
+        <f>IF('Revenue Schedule'!C2=0,0,C21/'Revenue Schedule'!C2)</f>
+        <v>13771.818181818182</v>
+      </c>
+      <c r="D30" s="36">
+        <f>IF('Revenue Schedule'!D2=0,0,D21/'Revenue Schedule'!D2)</f>
+        <v>14157.666666666666</v>
+      </c>
+      <c r="E30" s="36">
+        <f>IF('Revenue Schedule'!E2=0,0,E21/'Revenue Schedule'!E2)</f>
+        <v>14543.888888888889</v>
+      </c>
+      <c r="F30" s="36">
+        <f>IF('Revenue Schedule'!F2=0,0,F21/'Revenue Schedule'!F2)</f>
+        <v>14956</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B31" s="49">
-        <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
-        <v>0.17686567164179104</v>
+        <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
+        <v>0.32097512437810943</v>
       </c>
       <c r="C31" s="49">
-        <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
-        <v>0.13628952406099412</v>
+        <f>IF(C21=0,0,'Financial Model'!C3/C21)</f>
+        <v>0.2631922899201267</v>
       </c>
       <c r="D31" s="49">
-        <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
-        <v>0.11301532738445601</v>
+        <f>IF(D21=0,0,'Financial Model'!D3/D21)</f>
+        <v>0.19337932333482447</v>
       </c>
       <c r="E31" s="49">
-        <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
-        <v>0.10252874441346117</v>
+        <f>IF(E21=0,0,'Financial Model'!E3/E21)</f>
+        <v>0.16157607242446237</v>
       </c>
       <c r="F31" s="49">
-        <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
-        <v>0.09727032629045199</v>
+        <f>IF(F21=0,0,'Financial Model'!F3/F21)</f>
+        <v>0.1456539181599358</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="B32" s="12">
-        <f>IF(B20=0,0,B24/B20)</f>
-        <v>0.5021592039800995</v>
-      </c>
-      <c r="C32" s="12">
-        <f>IF(C20=0,0,C24/C20)</f>
-        <v>0.6005181860188792</v>
-      </c>
-      <c r="D32" s="12">
-        <f>IF(D20=0,0,D24/D20)</f>
-        <v>0.6936053492807195</v>
-      </c>
-      <c r="E32" s="12">
-        <f>IF(E20=0,0,E24/E20)</f>
-        <v>0.7358951831620765</v>
-      </c>
-      <c r="F32" s="12">
-        <f>IF(F20=0,0,F24/F20)</f>
-        <v>0.7570757555496122</v>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B35" s="49">
-        <v>0.4626865671641791</v>
-      </c>
-      <c r="C35" s="49">
-        <v>0.46326490197372766</v>
-      </c>
-      <c r="D35" s="49">
-        <v>0.46370635462529136</v>
-      </c>
-      <c r="E35" s="49">
-        <v>0.4645250009549639</v>
-      </c>
-      <c r="F35" s="49">
-        <v>0.4648970312917893</v>
-      </c>
+      <c r="A32" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B32" s="49">
+        <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
+        <v>0.19925373134328359</v>
+      </c>
+      <c r="C32" s="49">
+        <f>IF(C21=0,0,'Financial Model'!C4/C21)</f>
+        <v>0.15114198957026867</v>
+      </c>
+      <c r="D32" s="49">
+        <f>IF(D21=0,0,'Financial Model'!D4/D21)</f>
+        <v>0.12361029359828597</v>
+      </c>
+      <c r="E32" s="49">
+        <f>IF(E21=0,0,'Financial Model'!E4/E21)</f>
+        <v>0.11112341953474159</v>
+      </c>
+      <c r="F32" s="49">
+        <f>IF(F21=0,0,'Financial Model'!F4/F21)</f>
+        <v>0.10479239101364</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B33" s="12">
+        <f>IF(B21=0,0,B25/B21)</f>
+        <v>0.47977114427860695</v>
+      </c>
+      <c r="C33" s="12">
+        <f>IF(C21=0,0,C25/C21)</f>
+        <v>0.5856657205096046</v>
+      </c>
+      <c r="D33" s="12">
+        <f>IF(D21=0,0,D25/D21)</f>
+        <v>0.6830103830668895</v>
+      </c>
+      <c r="E33" s="12">
+        <f>IF(E21=0,0,E25/E21)</f>
+        <v>0.727300508040796</v>
+      </c>
+      <c r="F33" s="12">
+        <f>IF(F21=0,0,F25/F21)</f>
+        <v>0.7495536908264242</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B36" s="49">
-        <v>0.5223880597014925</v>
+        <v>0.4626865671641791</v>
       </c>
       <c r="C36" s="49">
-        <v>0.5235329064624727</v>
+        <v>0.46326490197372766</v>
       </c>
       <c r="D36" s="49">
-        <v>0.5245214606926754</v>
+        <v>0.46370635462529136</v>
       </c>
       <c r="E36" s="49">
-        <v>0.5259253600213912</v>
+        <v>0.4645250009549639</v>
       </c>
       <c r="F36" s="49">
-        <v>0.5267451190157796</v>
+        <v>0.4648970312917893</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B37" s="49">
+        <v>0.5223880597014925</v>
+      </c>
+      <c r="C37" s="49">
+        <v>0.5235329064624727</v>
+      </c>
+      <c r="D37" s="49">
+        <v>0.5245214606926754</v>
+      </c>
+      <c r="E37" s="49">
+        <v>0.5259253600213912</v>
+      </c>
+      <c r="F37" s="49">
+        <v>0.5267451190157796</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B38" s="49">
         <v>0.014925373134328358</v>
       </c>
-      <c r="C37" s="49">
+      <c r="C38" s="49">
         <v>0.01320219156379959</v>
       </c>
-      <c r="D37" s="49">
+      <c r="D38" s="49">
         <v>0.011772184682033292</v>
       </c>
-      <c r="E37" s="49">
+      <c r="E38" s="49">
         <v>0.009549639023644906</v>
       </c>
-      <c r="F37" s="49">
+      <c r="F38" s="49">
         <v>0.008357849692431132</v>
       </c>
     </row>
@@ -3851,7 +3934,7 @@
         <v>9</v>
       </c>
       <c r="C17" s="11">
-        <v>452913</v>
+        <v>448413</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
@@ -3859,7 +3942,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="12">
-        <v>0.7570757555496122</v>
+        <v>0.7495536908264242</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
@@ -3867,7 +3950,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="13">
-        <v>116.8966812773951</v>
+        <v>111.5836531466291</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
@@ -3972,7 +4055,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="47" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C2" s="47"/>
       <c r="D2" s="47"/>
@@ -3983,7 +4066,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="51" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="51"/>
@@ -3994,41 +4077,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="52" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" s="55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" s="55" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" s="55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" s="55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H6" s="55" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C7" s="56">
         <v>15</v>
@@ -4048,7 +4131,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C8" s="57">
         <v>201000</v>
@@ -4068,7 +4151,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C9" s="57">
         <v>64516</v>
@@ -4091,24 +4174,24 @@
         <v>17</v>
       </c>
       <c r="C10" s="57">
-        <v>35550</v>
+        <v>40050</v>
       </c>
       <c r="D10" s="57">
-        <v>41293</v>
+        <v>45793</v>
       </c>
       <c r="E10" s="57">
-        <v>48001</v>
+        <v>52501</v>
       </c>
       <c r="F10" s="57">
-        <v>53682</v>
+        <v>58182</v>
       </c>
       <c r="G10" s="57">
-        <v>58191</v>
+        <v>62691</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C11" s="57">
         <v>0</v>
@@ -4128,67 +4211,67 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="58" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C12" s="59">
-        <v>100934</v>
+        <v>96434</v>
       </c>
       <c r="D12" s="59">
-        <v>181945</v>
+        <v>177445</v>
       </c>
       <c r="E12" s="59">
-        <v>294595</v>
+        <v>290095</v>
       </c>
       <c r="F12" s="59">
-        <v>385300</v>
+        <v>380800</v>
       </c>
       <c r="G12" s="59">
-        <v>452913</v>
+        <v>448413</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="58" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C13" s="59">
-        <v>100934</v>
+        <v>96434</v>
       </c>
       <c r="D13" s="59">
-        <v>282879</v>
+        <v>273879</v>
       </c>
       <c r="E13" s="59">
-        <v>577474</v>
+        <v>563974</v>
       </c>
       <c r="F13" s="59">
-        <v>962774</v>
+        <v>944774</v>
       </c>
       <c r="G13" s="59">
-        <v>1415687</v>
+        <v>1393187</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="58" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C14" s="60">
-        <v>0.5021592039800995</v>
+        <v>0.47977114427860695</v>
       </c>
       <c r="D14" s="60">
-        <v>0.6005181860188792</v>
+        <v>0.5856657205096046</v>
       </c>
       <c r="E14" s="60">
-        <v>0.6936053492807195</v>
+        <v>0.6830103830668895</v>
       </c>
       <c r="F14" s="60">
-        <v>0.7358951831620765</v>
+        <v>0.727300508040796</v>
       </c>
       <c r="G14" s="60">
-        <v>0.7570757555496122</v>
+        <v>0.7495536908264242</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="58" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C15" s="61">
         <v>13400</v>
@@ -4206,32 +4289,32 @@
         <v>14956</v>
       </c>
       <c r="H15" s="62" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="58" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C16" s="63">
-        <v>6671.066666666667</v>
+        <v>6971.066666666667</v>
       </c>
       <c r="D16" s="63">
-        <v>5501.590909090909</v>
+        <v>5706.136363636364</v>
       </c>
       <c r="E16" s="63">
-        <v>4337.833333333333</v>
+        <v>4487.833333333333</v>
       </c>
       <c r="F16" s="63">
-        <v>3841.1111111111113</v>
+        <v>3966.1111111111113</v>
       </c>
       <c r="G16" s="63">
-        <v>3633.175</v>
+        <v>3745.675</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C17" s="57">
         <v>400</v>
@@ -4251,7 +4334,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C18" s="61">
         <v>1720</v>
@@ -4269,32 +4352,32 @@
         <v>723.7497574000001</v>
       </c>
       <c r="H18" s="62" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="58" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C19" s="64">
-        <v>6728.933333333333</v>
+        <v>6428.933333333333</v>
       </c>
       <c r="D19" s="64">
-        <v>8270.227272727272</v>
+        <v>8065.681818181818</v>
       </c>
       <c r="E19" s="64">
-        <v>9819.833333333334</v>
+        <v>9669.833333333334</v>
       </c>
       <c r="F19" s="64">
-        <v>10702.777777777777</v>
+        <v>10577.777777777777</v>
       </c>
       <c r="G19" s="64">
-        <v>11322.825</v>
+        <v>11210.325</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="58" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C20" s="60">
         <v>0.32097512437810943</v>
@@ -4312,12 +4395,12 @@
         <v>0.1456539181599358</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="58" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C21" s="60">
         <v>0.12835820895522387</v>
@@ -4335,35 +4418,35 @@
         <v>0.048391933498261576</v>
       </c>
       <c r="H21" s="62" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="58" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C22" s="60">
-        <v>0.5021592039800995</v>
+        <v>0.47977114427860695</v>
       </c>
       <c r="D22" s="60">
-        <v>0.6005181860188792</v>
+        <v>0.5856657205096046</v>
       </c>
       <c r="E22" s="60">
-        <v>0.6936053492807195</v>
+        <v>0.6830103830668895</v>
       </c>
       <c r="F22" s="60">
-        <v>0.7358951831620765</v>
+        <v>0.727300508040796</v>
       </c>
       <c r="G22" s="60">
-        <v>0.7570757555496122</v>
+        <v>0.7495536908264242</v>
       </c>
       <c r="H22" s="62" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="58" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C23" s="65">
         <v>3</v>
@@ -4381,35 +4464,35 @@
         <v>3</v>
       </c>
       <c r="H23" s="62" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="58" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E24" s="66" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F24" s="66" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G24" s="66" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="58" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C25" s="45" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
@@ -4432,170 +4515,170 @@
         <v>0</v>
       </c>
       <c r="H25" s="62" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="58" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C26" s="68">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="65">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E26" s="65">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F26" s="69" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G26" s="69" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H26" s="62" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="58" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C27" s="65">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="D27" s="65">
-        <v>853</v>
+        <v>796</v>
       </c>
       <c r="E27" s="65">
-        <v>1620</v>
+        <v>1529</v>
       </c>
       <c r="F27" s="65">
-        <v>2541</v>
+        <v>2415</v>
       </c>
       <c r="G27" s="65">
-        <v>3556</v>
+        <v>3394</v>
       </c>
       <c r="H27" s="62" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="70" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D30" s="71" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E30" s="71"/>
       <c r="F30" s="72" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G30" s="72"/>
       <c r="H30" s="72"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="70" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D31" s="71" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E31" s="71"/>
       <c r="F31" s="72" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G31" s="72"/>
       <c r="H31" s="72"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="70" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D32" s="71" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E32" s="71"/>
       <c r="F32" s="72" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G32" s="72"/>
       <c r="H32" s="72"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="70" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D33" s="71" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E33" s="71"/>
       <c r="F33" s="72" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G33" s="72"/>
       <c r="H33" s="72"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="70" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C34" s="45" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D34" s="71" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E34" s="71"/>
       <c r="F34" s="72" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G34" s="72"/>
       <c r="H34" s="72"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="70" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D35" s="71" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E35" s="71"/>
       <c r="F35" s="72" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G35" s="72"/>
       <c r="H35" s="72"/>
@@ -4605,7 +4688,7 @@
         <v>20</v>
       </c>
       <c r="C37" s="58" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D37" s="58"/>
       <c r="E37" s="58"/>
@@ -4613,7 +4696,7 @@
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="73" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C39" s="73"/>
       <c r="D39" s="73"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -528,7 +528,7 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -528,7 +528,7 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -654,7 +654,7 @@
     <t>The model reaches profit early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -1990,7 +1990,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:I39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2000,7 +2000,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="47" t="s">
         <v>161</v>
       </c>
@@ -2010,8 +2010,9 @@
       <c r="F2" s="47"/>
       <c r="G2" s="47"/>
       <c r="H2" s="47"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="47"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
         <v>162</v>
       </c>
@@ -2021,6 +2022,7 @@
       <c r="F3" s="53"/>
       <c r="G3" s="53"/>
       <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="54" t="s">
@@ -2511,7 +2513,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
         <v>197</v>
       </c>
@@ -2527,8 +2529,9 @@
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="72" t="s">
         <v>201</v>
       </c>
@@ -2544,8 +2547,9 @@
       </c>
       <c r="G30" s="74"/>
       <c r="H30" s="74"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="74"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="72" t="s">
         <v>205</v>
       </c>
@@ -2561,8 +2565,9 @@
       </c>
       <c r="G31" s="74"/>
       <c r="H31" s="74"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="74"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="72" t="s">
         <v>208</v>
       </c>
@@ -2578,8 +2583,9 @@
       </c>
       <c r="G32" s="74"/>
       <c r="H32" s="74"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="74"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="72" t="s">
         <v>211</v>
       </c>
@@ -2595,8 +2601,9 @@
       </c>
       <c r="G33" s="74"/>
       <c r="H33" s="74"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="74"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="72" t="s">
         <v>214</v>
       </c>
@@ -2612,8 +2619,9 @@
       </c>
       <c r="G34" s="74"/>
       <c r="H34" s="74"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="74"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="72" t="s">
         <v>217</v>
       </c>
@@ -2629,6 +2637,7 @@
       </c>
       <c r="G35" s="74"/>
       <c r="H35" s="74"/>
+      <c r="I35" s="74"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="72" t="s">
@@ -2641,7 +2650,7 @@
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="75" t="s">
         <v>221</v>
       </c>
@@ -2651,27 +2660,28 @@
       <c r="F39" s="75"/>
       <c r="G39" s="75"/>
       <c r="H39" s="75"/>
+      <c r="I39" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B39:I39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -20,19 +20,19 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staffing &amp; Personnel'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Operating Expenses'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Capital &amp; Debt'!$A1:$F4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$G16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="235">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 7, 2026</t>
+    <t>May 9, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -399,6 +399,27 @@
     <t>Total Personnel Cost</t>
   </si>
   <si>
+    <t>FOUNDER COMPENSATION</t>
+  </si>
+  <si>
+    <t>5-Year Total</t>
+  </si>
+  <si>
+    <t>Founder Compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Fully-loaded (incl. benefits + payroll tax)</t>
+  </si>
+  <si>
+    <t>Founder Compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t>Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market rate ("sweat equity"). Lenders and boards underwrite to the market-rate line; the adjustment shows the gap.</t>
+  </si>
+  <si>
     <t>INSTRUCTIONAL / PROGRAM</t>
   </si>
   <si>
@@ -468,6 +489,21 @@
     <t>Cumulative Profit</t>
   </si>
   <si>
+    <t>FOUNDER COMPENSATION (memo — already in Personnel above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market ("sweat equity"). Lenders / boards underwrite to the market-rate line.</t>
+  </si>
+  <si>
     <t>Break-even</t>
   </si>
   <si>
@@ -528,7 +564,10 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
+  </si>
+  <si>
+    <t>Built from assumptions</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -720,7 +759,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -823,6 +862,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="16"/>
@@ -844,6 +889,13 @@
       <i/>
       <color rgb="FF6B7280"/>
       <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -966,7 +1018,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1015,6 +1067,12 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1022,20 +1080,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1055,7 +1114,7 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1081,7 +1140,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1990,7 +2049,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I39"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2001,673 +2060,684 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="47" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
+      <c r="B2" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="54" t="s">
-        <v>163</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="56" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="57" t="s">
+      <c r="B3" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="56" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="57" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="F5" s="59" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="57" t="s">
+      <c r="D7" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="E7" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="F7" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G7" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="57" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="58">
-        <v>15</v>
-      </c>
-      <c r="D7" s="58">
-        <v>22</v>
-      </c>
-      <c r="E7" s="58">
-        <v>30</v>
-      </c>
-      <c r="F7" s="58">
-        <v>36</v>
-      </c>
-      <c r="G7" s="58">
-        <v>40</v>
+      <c r="H7" s="60" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="59">
-        <v>201000</v>
-      </c>
-      <c r="D8" s="59">
-        <v>302980</v>
-      </c>
-      <c r="E8" s="59">
-        <v>424730</v>
-      </c>
-      <c r="F8" s="59">
-        <v>523580</v>
-      </c>
-      <c r="G8" s="59">
-        <v>598240</v>
+        <v>181</v>
+      </c>
+      <c r="C8" s="61">
+        <v>15</v>
+      </c>
+      <c r="D8" s="61">
+        <v>22</v>
+      </c>
+      <c r="E8" s="61">
+        <v>30</v>
+      </c>
+      <c r="F8" s="61">
+        <v>36</v>
+      </c>
+      <c r="G8" s="61">
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="59">
-        <v>64516</v>
-      </c>
-      <c r="D9" s="59">
-        <v>79742</v>
-      </c>
-      <c r="E9" s="59">
-        <v>82134</v>
-      </c>
-      <c r="F9" s="59">
-        <v>84598</v>
-      </c>
-      <c r="G9" s="59">
-        <v>87136</v>
+        <v>182</v>
+      </c>
+      <c r="C9" s="62">
+        <v>201000</v>
+      </c>
+      <c r="D9" s="62">
+        <v>302980</v>
+      </c>
+      <c r="E9" s="62">
+        <v>424730</v>
+      </c>
+      <c r="F9" s="62">
+        <v>523580</v>
+      </c>
+      <c r="G9" s="62">
+        <v>598240</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="59">
-        <v>40050</v>
-      </c>
-      <c r="D10" s="59">
-        <v>45793</v>
-      </c>
-      <c r="E10" s="59">
-        <v>52501</v>
-      </c>
-      <c r="F10" s="59">
-        <v>58182</v>
-      </c>
-      <c r="G10" s="59">
-        <v>62691</v>
+        <v>183</v>
+      </c>
+      <c r="C10" s="62">
+        <v>64516</v>
+      </c>
+      <c r="D10" s="62">
+        <v>79742</v>
+      </c>
+      <c r="E10" s="62">
+        <v>82134</v>
+      </c>
+      <c r="F10" s="62">
+        <v>84598</v>
+      </c>
+      <c r="G10" s="62">
+        <v>87136</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C11" s="59">
+        <v>17</v>
+      </c>
+      <c r="C11" s="62">
+        <v>40050</v>
+      </c>
+      <c r="D11" s="62">
+        <v>45793</v>
+      </c>
+      <c r="E11" s="62">
+        <v>52501</v>
+      </c>
+      <c r="F11" s="62">
+        <v>58182</v>
+      </c>
+      <c r="G11" s="62">
+        <v>62691</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="62">
         <v>0</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D12" s="62">
         <v>0</v>
       </c>
-      <c r="E11" s="59">
+      <c r="E12" s="62">
         <v>0</v>
       </c>
-      <c r="F11" s="59">
+      <c r="F12" s="62">
         <v>0</v>
       </c>
-      <c r="G11" s="59">
+      <c r="G12" s="62">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="60" t="s">
-        <v>172</v>
-      </c>
-      <c r="C12" s="61">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="64">
         <v>96434</v>
       </c>
-      <c r="D12" s="61">
+      <c r="D13" s="64">
         <v>177445</v>
       </c>
-      <c r="E12" s="61">
+      <c r="E13" s="64">
         <v>290095</v>
       </c>
-      <c r="F12" s="61">
+      <c r="F13" s="64">
         <v>380800</v>
       </c>
-      <c r="G12" s="61">
+      <c r="G13" s="64">
         <v>448413</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="60" t="s">
-        <v>173</v>
-      </c>
-      <c r="C13" s="61">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="64">
         <v>96434</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D14" s="64">
         <v>273879</v>
       </c>
-      <c r="E13" s="61">
+      <c r="E14" s="64">
         <v>563974</v>
       </c>
-      <c r="F13" s="61">
+      <c r="F14" s="64">
         <v>944774</v>
       </c>
-      <c r="G13" s="61">
+      <c r="G14" s="64">
         <v>1393187</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="60" t="s">
-        <v>174</v>
-      </c>
-      <c r="C14" s="62">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="65">
         <v>0.47977114427860695</v>
       </c>
-      <c r="D14" s="62">
+      <c r="D15" s="65">
         <v>0.5856657205096046</v>
       </c>
-      <c r="E14" s="62">
+      <c r="E15" s="65">
         <v>0.6830103830668895</v>
       </c>
-      <c r="F14" s="62">
+      <c r="F15" s="65">
         <v>0.727300508040796</v>
       </c>
-      <c r="G14" s="62">
+      <c r="G15" s="65">
         <v>0.7495536908264242</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="C15" s="63">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" s="66">
         <v>13400</v>
       </c>
-      <c r="D15" s="63">
+      <c r="D16" s="66">
         <v>13771.818181818182</v>
       </c>
-      <c r="E15" s="63">
+      <c r="E16" s="66">
         <v>14157.666666666666</v>
       </c>
-      <c r="F15" s="63">
+      <c r="F16" s="66">
         <v>14543.888888888889</v>
       </c>
-      <c r="G15" s="63">
+      <c r="G16" s="66">
         <v>14956</v>
       </c>
-      <c r="H15" s="64" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="60" t="s">
-        <v>176</v>
-      </c>
-      <c r="C16" s="65">
+      <c r="H16" s="67" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="63" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="68">
         <v>6971.066666666667</v>
       </c>
-      <c r="D16" s="65">
+      <c r="D17" s="68">
         <v>5706.136363636364</v>
       </c>
-      <c r="E16" s="65">
+      <c r="E17" s="68">
         <v>4487.833333333333</v>
       </c>
-      <c r="F16" s="65">
+      <c r="F17" s="68">
         <v>3966.1111111111113</v>
       </c>
-      <c r="G16" s="65">
+      <c r="G17" s="68">
         <v>3745.675</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C17" s="59">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C18" s="62">
         <v>400</v>
       </c>
-      <c r="D17" s="59">
+      <c r="D18" s="62">
         <v>412</v>
       </c>
-      <c r="E17" s="59">
+      <c r="E18" s="62">
         <v>424</v>
       </c>
-      <c r="F17" s="59">
+      <c r="F18" s="62">
         <v>437</v>
       </c>
-      <c r="G17" s="59">
+      <c r="G18" s="62">
         <v>450</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C18" s="63">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="66">
         <v>1720</v>
       </c>
-      <c r="D18" s="63">
+      <c r="D19" s="66">
         <v>1206.9545454545455</v>
       </c>
-      <c r="E18" s="63">
+      <c r="E19" s="66">
         <v>910.8813333333333</v>
       </c>
-      <c r="F18" s="63">
+      <c r="F19" s="66">
         <v>781.1362</v>
       </c>
-      <c r="G18" s="63">
+      <c r="G19" s="66">
         <v>723.7497574000001</v>
       </c>
-      <c r="H18" s="64" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="60" t="s">
-        <v>180</v>
-      </c>
-      <c r="C19" s="66">
+      <c r="H19" s="67" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="69">
         <v>6428.933333333333</v>
       </c>
-      <c r="D19" s="66">
+      <c r="D20" s="69">
         <v>8065.681818181818</v>
       </c>
-      <c r="E19" s="66">
+      <c r="E20" s="69">
         <v>9669.833333333334</v>
       </c>
-      <c r="F19" s="66">
+      <c r="F20" s="69">
         <v>10577.777777777777</v>
       </c>
-      <c r="G19" s="66">
+      <c r="G20" s="69">
         <v>11210.325</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="60" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="62">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="63" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" s="65">
         <v>0.32097512437810943</v>
       </c>
-      <c r="D20" s="62">
+      <c r="D21" s="65">
         <v>0.2631922899201267</v>
       </c>
-      <c r="E20" s="62">
+      <c r="E21" s="65">
         <v>0.19337932333482447</v>
       </c>
-      <c r="F20" s="62">
+      <c r="F21" s="65">
         <v>0.16157607242446237</v>
       </c>
-      <c r="G20" s="62">
+      <c r="G21" s="65">
         <v>0.1456539181599358</v>
       </c>
-      <c r="H20" s="64" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="60" t="s">
-        <v>183</v>
-      </c>
-      <c r="C21" s="62">
+      <c r="H21" s="67" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="63" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="65">
         <v>0.12835820895522387</v>
       </c>
-      <c r="D21" s="62">
+      <c r="D22" s="65">
         <v>0.08763944814839263</v>
       </c>
-      <c r="E21" s="62">
+      <c r="E22" s="65">
         <v>0.06433837967650036</v>
       </c>
-      <c r="F21" s="62">
+      <c r="F22" s="65">
         <v>0.05370889491577219</v>
       </c>
-      <c r="G21" s="62">
+      <c r="G22" s="65">
         <v>0.048391933498261576</v>
       </c>
-      <c r="H21" s="64" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="60" t="s">
-        <v>185</v>
-      </c>
-      <c r="C22" s="62">
+      <c r="H22" s="67" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" s="65">
         <v>0.47977114427860695</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D23" s="65">
         <v>0.5856657205096046</v>
       </c>
-      <c r="E22" s="62">
+      <c r="E23" s="65">
         <v>0.6830103830668895</v>
       </c>
-      <c r="F22" s="62">
+      <c r="F23" s="65">
         <v>0.727300508040796</v>
       </c>
-      <c r="G22" s="62">
+      <c r="G23" s="65">
         <v>0.7495536908264242</v>
       </c>
-      <c r="H22" s="64" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="60" t="s">
-        <v>187</v>
-      </c>
-      <c r="C23" s="67">
+      <c r="H23" s="67" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="70">
         <v>3</v>
       </c>
-      <c r="D23" s="67">
+      <c r="D24" s="70">
         <v>3</v>
       </c>
-      <c r="E23" s="67">
+      <c r="E24" s="70">
         <v>3</v>
       </c>
-      <c r="F23" s="67">
+      <c r="F24" s="70">
         <v>3</v>
       </c>
-      <c r="G23" s="67">
+      <c r="G24" s="70">
         <v>3</v>
       </c>
-      <c r="H23" s="64" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="60" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="68" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" s="68" t="s">
-        <v>190</v>
-      </c>
-      <c r="E24" s="68" t="s">
-        <v>190</v>
-      </c>
-      <c r="F24" s="68" t="s">
-        <v>190</v>
-      </c>
-      <c r="G24" s="68" t="s">
-        <v>190</v>
-      </c>
-      <c r="H24" s="64" t="s">
-        <v>190</v>
+      <c r="H24" s="67" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="60" t="s">
-        <v>191</v>
-      </c>
-      <c r="C25" s="45" t="str">
+      <c r="B25" s="63" t="s">
+        <v>202</v>
+      </c>
+      <c r="C25" s="71" t="s">
+        <v>203</v>
+      </c>
+      <c r="D25" s="71" t="s">
+        <v>203</v>
+      </c>
+      <c r="E25" s="71" t="s">
+        <v>203</v>
+      </c>
+      <c r="F25" s="71" t="s">
+        <v>203</v>
+      </c>
+      <c r="G25" s="71" t="s">
+        <v>203</v>
+      </c>
+      <c r="H25" s="67" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="C26" s="47" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="69" t="str">
+      <c r="D26" s="72" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="69" t="str">
+      <c r="E26" s="72" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="69" t="str">
+      <c r="F26" s="72" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="69" t="str">
+      <c r="G26" s="72" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="64" t="s">
+      <c r="H26" s="67" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="60" t="s">
-        <v>192</v>
-      </c>
-      <c r="C26" s="70">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="C27" s="73">
         <v>11</v>
       </c>
-      <c r="D26" s="67">
+      <c r="D27" s="70">
         <v>26</v>
       </c>
-      <c r="E26" s="67">
+      <c r="E27" s="70">
         <v>50</v>
       </c>
-      <c r="F26" s="71" t="s">
-        <v>193</v>
-      </c>
-      <c r="G26" s="71" t="s">
-        <v>193</v>
-      </c>
-      <c r="H26" s="64" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="60" t="s">
-        <v>195</v>
-      </c>
-      <c r="C27" s="67">
+      <c r="F27" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="G27" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="H27" s="67" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="70">
         <v>337</v>
       </c>
-      <c r="D27" s="67">
+      <c r="D28" s="70">
         <v>796</v>
       </c>
-      <c r="E27" s="67">
+      <c r="E28" s="70">
         <v>1529</v>
       </c>
-      <c r="F27" s="67">
+      <c r="F28" s="70">
         <v>2415</v>
       </c>
-      <c r="G27" s="67">
+      <c r="G28" s="70">
         <v>3394</v>
       </c>
-      <c r="H27" s="64" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="72" t="s">
-        <v>201</v>
-      </c>
-      <c r="C30" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="D30" s="73" t="s">
-        <v>203</v>
-      </c>
-      <c r="E30" s="73"/>
-      <c r="F30" s="74" t="s">
-        <v>204</v>
-      </c>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
+      <c r="H28" s="67" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="72" t="s">
-        <v>205</v>
-      </c>
-      <c r="C31" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="D31" s="73" t="s">
-        <v>206</v>
-      </c>
-      <c r="E31" s="73"/>
-      <c r="F31" s="74" t="s">
-        <v>207</v>
-      </c>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
+      <c r="B31" s="75" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="D31" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="76"/>
+      <c r="F31" s="77" t="s">
+        <v>217</v>
+      </c>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="72" t="s">
-        <v>208</v>
-      </c>
-      <c r="C32" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="D32" s="73" t="s">
-        <v>209</v>
-      </c>
-      <c r="E32" s="73"/>
-      <c r="F32" s="74" t="s">
-        <v>210</v>
-      </c>
-      <c r="G32" s="74"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
+      <c r="B32" s="75" t="s">
+        <v>218</v>
+      </c>
+      <c r="C32" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="D32" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="E32" s="76"/>
+      <c r="F32" s="77" t="s">
+        <v>220</v>
+      </c>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="72" t="s">
-        <v>211</v>
-      </c>
-      <c r="C33" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="D33" s="73" t="s">
-        <v>212</v>
-      </c>
-      <c r="E33" s="73"/>
-      <c r="F33" s="74" t="s">
-        <v>213</v>
-      </c>
-      <c r="G33" s="74"/>
-      <c r="H33" s="74"/>
-      <c r="I33" s="74"/>
+      <c r="B33" s="75" t="s">
+        <v>221</v>
+      </c>
+      <c r="C33" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="D33" s="76" t="s">
+        <v>222</v>
+      </c>
+      <c r="E33" s="76"/>
+      <c r="F33" s="77" t="s">
+        <v>223</v>
+      </c>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="72" t="s">
-        <v>214</v>
-      </c>
-      <c r="C34" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="D34" s="73" t="s">
+      <c r="B34" s="75" t="s">
+        <v>224</v>
+      </c>
+      <c r="C34" s="47" t="s">
         <v>215</v>
       </c>
-      <c r="E34" s="73"/>
-      <c r="F34" s="74" t="s">
-        <v>216</v>
-      </c>
-      <c r="G34" s="74"/>
-      <c r="H34" s="74"/>
-      <c r="I34" s="74"/>
+      <c r="D34" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="E34" s="76"/>
+      <c r="F34" s="77" t="s">
+        <v>226</v>
+      </c>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="72" t="s">
-        <v>217</v>
-      </c>
-      <c r="C35" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="D35" s="73" t="s">
-        <v>218</v>
-      </c>
-      <c r="E35" s="73"/>
-      <c r="F35" s="74" t="s">
-        <v>219</v>
-      </c>
-      <c r="G35" s="74"/>
-      <c r="H35" s="74"/>
-      <c r="I35" s="74"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="72" t="s">
+      <c r="B35" s="75" t="s">
+        <v>227</v>
+      </c>
+      <c r="C35" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="D35" s="76" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" s="76"/>
+      <c r="F35" s="77" t="s">
+        <v>229</v>
+      </c>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
+      <c r="I35" s="77"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B36" s="75" t="s">
+        <v>230</v>
+      </c>
+      <c r="C36" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="D36" s="76" t="s">
+        <v>231</v>
+      </c>
+      <c r="E36" s="76"/>
+      <c r="F36" s="77" t="s">
+        <v>232</v>
+      </c>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="60" t="s">
-        <v>220</v>
-      </c>
-      <c r="D37" s="60"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="60"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="75" t="s">
-        <v>221</v>
-      </c>
-      <c r="C39" s="75"/>
-      <c r="D39" s="75"/>
-      <c r="E39" s="75"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
+      <c r="C38" s="63" t="s">
+        <v>233</v>
+      </c>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="78" t="s">
+        <v>234</v>
+      </c>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
@@ -2680,84 +2750,86 @@
     <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="F35:I35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
-  <conditionalFormatting sqref="C12:G12">
+  <conditionalFormatting sqref="C13:G13">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C12&gt;=0</formula>
+      <formula>C13&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C12&gt;=-1</formula>
+      <formula>C13&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C12&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13:G13">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C13&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C13&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C13&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:G14">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C14&gt;=0.05</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>C14&gt;=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C14&lt;0</formula>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C14&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C14&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C15&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C15&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C15&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&gt;=10000</formula>
+      <formula>C16&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&gt;=7000</formula>
+      <formula>C16&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&lt;7000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:G21">
-    <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C21&lt;=0.55</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C21&lt;=0.65</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C21&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:G22">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C22&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C22&lt;=0.22</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C22&gt;0.22</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23:G23">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C23&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C23&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C23&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3066,11 +3138,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3352,9 +3424,154 @@
         <v>87136</v>
       </c>
     </row>
+    <row r="23" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" s="36">
+        <v>48000</v>
+      </c>
+      <c r="C24" s="36">
+        <v>49440</v>
+      </c>
+      <c r="D24" s="36">
+        <v>50923</v>
+      </c>
+      <c r="E24" s="36">
+        <v>52451</v>
+      </c>
+      <c r="F24" s="36">
+        <v>54024</v>
+      </c>
+      <c r="G24" s="36">
+        <f>SUM(B24:F24)</f>
+        <v>254838</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="36">
+        <v>61272</v>
+      </c>
+      <c r="C25" s="36">
+        <v>63110</v>
+      </c>
+      <c r="D25" s="36">
+        <v>65003</v>
+      </c>
+      <c r="E25" s="36">
+        <v>66954</v>
+      </c>
+      <c r="F25" s="36">
+        <v>68962</v>
+      </c>
+      <c r="G25" s="36">
+        <f>SUM(B25:F25)</f>
+        <v>325301</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="36">
+        <v>50000</v>
+      </c>
+      <c r="C26" s="36">
+        <v>52000</v>
+      </c>
+      <c r="D26" s="36">
+        <v>53000</v>
+      </c>
+      <c r="E26" s="36">
+        <v>55000</v>
+      </c>
+      <c r="F26" s="36">
+        <v>56000</v>
+      </c>
+      <c r="G26" s="36">
+        <f>SUM(B26:F26)</f>
+        <v>266000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="36">
+        <v>63825</v>
+      </c>
+      <c r="C27" s="36">
+        <v>66378</v>
+      </c>
+      <c r="D27" s="36">
+        <v>67655</v>
+      </c>
+      <c r="E27" s="36">
+        <v>70208</v>
+      </c>
+      <c r="F27" s="36">
+        <v>71484</v>
+      </c>
+      <c r="G27" s="36">
+        <f>SUM(B27:F27)</f>
+        <v>339550</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="10">
+        <v>2553</v>
+      </c>
+      <c r="C28" s="10">
+        <v>3268</v>
+      </c>
+      <c r="D28" s="10">
+        <v>2651</v>
+      </c>
+      <c r="E28" s="10">
+        <v>3254</v>
+      </c>
+      <c r="F28" s="10">
+        <v>2522</v>
+      </c>
+      <c r="G28" s="10">
+        <f>SUM(B28:F28)</f>
+        <v>14248</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1" spans="1:7" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -3424,7 +3641,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -3434,7 +3651,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B4" s="36">
         <f>400*Assumptions!B23</f>
@@ -3459,7 +3676,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B5" s="37">
         <f>SUM(B4:B4)</f>
@@ -3484,7 +3701,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3494,7 +3711,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B7" s="36">
         <f>250*Assumptions!B23</f>
@@ -3519,7 +3736,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B8" s="37">
         <f>SUM(B7:B7)</f>
@@ -3544,7 +3761,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3554,7 +3771,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B10" s="36">
         <f>1800*12</f>
@@ -3579,7 +3796,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B11" s="36">
         <f>200*12</f>
@@ -3604,7 +3821,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B12" s="36">
         <v>1800</v>
@@ -3624,7 +3841,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B13" s="37">
         <f>SUM(B10:B12)</f>
@@ -3649,7 +3866,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3659,7 +3876,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B15" s="36">
         <v>4500</v>
@@ -3679,7 +3896,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B16" s="37">
         <f>SUM(B15:B15)</f>
@@ -3704,7 +3921,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B18" s="37">
         <f>B5+B8+B13+B16</f>
@@ -3771,7 +3988,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3781,7 +3998,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B3" s="36">
         <v>0</v>
@@ -3801,7 +4018,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B4" s="37">
         <v>0</v>
@@ -3834,11 +4051,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3863,7 +4080,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B2" s="36">
         <f>'Revenue Schedule'!B14</f>
@@ -3888,7 +4105,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B3" s="36">
         <f>'Staffing &amp; Personnel'!B21</f>
@@ -3963,7 +4180,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B6" s="37">
         <f>B3+B4+B5</f>
@@ -3988,7 +4205,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B7" s="37">
         <f>B2-B6</f>
@@ -4013,7 +4230,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B8" s="36">
         <f>B7</f>
@@ -4040,48 +4257,147 @@
       <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="44">
+      <c r="B9" s="46">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>11.066771225828662</v>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="46">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>26.180332178276974</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="46">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>50.26692910461618</v>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="46">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>79.40389410281551</v>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="46">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>111.5836531466291</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="46" t="s">
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="36">
+        <v>61272</v>
+      </c>
+      <c r="C12" s="36">
+        <v>63110</v>
+      </c>
+      <c r="D12" s="36">
+        <v>65003</v>
+      </c>
+      <c r="E12" s="36">
+        <v>66954</v>
+      </c>
+      <c r="F12" s="36">
+        <v>68962</v>
+      </c>
+      <c r="G12" s="36">
+        <f>SUM(B12:F12)</f>
+        <v>325301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" s="36">
+        <v>63825</v>
+      </c>
+      <c r="C13" s="36">
+        <v>66378</v>
+      </c>
+      <c r="D13" s="36">
+        <v>67655</v>
+      </c>
+      <c r="E13" s="36">
+        <v>70208</v>
+      </c>
+      <c r="F13" s="36">
+        <v>71484</v>
+      </c>
+      <c r="G13" s="36">
+        <f>SUM(B13:F13)</f>
+        <v>339550</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="10">
+        <v>2553</v>
+      </c>
+      <c r="C14" s="10">
+        <v>3268</v>
+      </c>
+      <c r="D14" s="10">
+        <v>2651</v>
+      </c>
+      <c r="E14" s="10">
+        <v>3254</v>
+      </c>
+      <c r="F14" s="10">
+        <v>2522</v>
+      </c>
+      <c r="G14" s="10">
+        <f>SUM(B14:F14)</f>
+        <v>14248</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:7" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D16" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E16" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F16" s="48" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:G15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -4104,18 +4420,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="A1" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
-        <v>145</v>
+      <c r="A2" s="50" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4197,12 +4513,12 @@
         <v>41</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -4257,24 +4573,24 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="49">
+        <v>161</v>
+      </c>
+      <c r="C18" s="51">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
         <v>0.4666666666666667</v>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="51">
         <f>IF(C17=0,0,(D17-C17)/C17)</f>
         <v>0.36363636363636365</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="51">
         <f>IF(D17=0,0,(E17-D17)/D17)</f>
         <v>0.2</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="51">
         <f>IF(E17=0,0,(F17-E17)/E17)</f>
         <v>0.1111111111111111</v>
       </c>
@@ -4301,7 +4617,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B21" s="36">
         <f>'Financial Model'!B2</f>
@@ -4326,7 +4642,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B22" s="36">
         <f>'Financial Model'!B3</f>
@@ -4376,7 +4692,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B24" s="37">
         <f>'Financial Model'!B6</f>
@@ -4401,32 +4717,32 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="B25" s="50">
+        <v>147</v>
+      </c>
+      <c r="B25" s="52">
         <f>'Financial Model'!B7</f>
         <v>96434</v>
       </c>
-      <c r="C25" s="50">
+      <c r="C25" s="52">
         <f>'Financial Model'!C7</f>
         <v>177445</v>
       </c>
-      <c r="D25" s="50">
+      <c r="D25" s="52">
         <f>'Financial Model'!D7</f>
         <v>290095</v>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>'Financial Model'!E7</f>
         <v>380800</v>
       </c>
-      <c r="F25" s="50">
+      <c r="F25" s="52">
         <f>'Financial Model'!F7</f>
         <v>448413</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B26" s="36">
         <f>'Financial Model'!B8</f>
@@ -4476,7 +4792,7 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -4486,7 +4802,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B30" s="36">
         <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
@@ -4511,57 +4827,57 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="B31" s="49">
+        <v>164</v>
+      </c>
+      <c r="B31" s="51">
         <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
         <v>0.32097512437810943</v>
       </c>
-      <c r="C31" s="49">
+      <c r="C31" s="51">
         <f>IF(C21=0,0,'Financial Model'!C3/C21)</f>
         <v>0.2631922899201267</v>
       </c>
-      <c r="D31" s="49">
+      <c r="D31" s="51">
         <f>IF(D21=0,0,'Financial Model'!D3/D21)</f>
         <v>0.19337932333482447</v>
       </c>
-      <c r="E31" s="49">
+      <c r="E31" s="51">
         <f>IF(E21=0,0,'Financial Model'!E3/E21)</f>
         <v>0.16157607242446237</v>
       </c>
-      <c r="F31" s="49">
+      <c r="F31" s="51">
         <f>IF(F21=0,0,'Financial Model'!F3/F21)</f>
         <v>0.1456539181599358</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="B32" s="49">
+        <v>165</v>
+      </c>
+      <c r="B32" s="51">
         <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
         <v>0.19925373134328359</v>
       </c>
-      <c r="C32" s="49">
+      <c r="C32" s="51">
         <f>IF(C21=0,0,'Financial Model'!C4/C21)</f>
         <v>0.15114198957026867</v>
       </c>
-      <c r="D32" s="49">
+      <c r="D32" s="51">
         <f>IF(D21=0,0,'Financial Model'!D4/D21)</f>
         <v>0.12361029359828597</v>
       </c>
-      <c r="E32" s="49">
+      <c r="E32" s="51">
         <f>IF(E21=0,0,'Financial Model'!E4/E21)</f>
         <v>0.11112341953474159</v>
       </c>
-      <c r="F32" s="49">
+      <c r="F32" s="51">
         <f>IF(F21=0,0,'Financial Model'!F4/F21)</f>
         <v>0.10479239101364</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B33" s="12">
         <f>IF(B21=0,0,B25/B21)</f>
@@ -4586,7 +4902,7 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -4596,61 +4912,61 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="B36" s="49">
+        <v>168</v>
+      </c>
+      <c r="B36" s="51">
         <v>0.4626865671641791</v>
       </c>
-      <c r="C36" s="49">
+      <c r="C36" s="51">
         <v>0.46326490197372766</v>
       </c>
-      <c r="D36" s="49">
+      <c r="D36" s="51">
         <v>0.46370635462529136</v>
       </c>
-      <c r="E36" s="49">
+      <c r="E36" s="51">
         <v>0.4645250009549639</v>
       </c>
-      <c r="F36" s="49">
+      <c r="F36" s="51">
         <v>0.4648970312917893</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="B37" s="49">
+        <v>169</v>
+      </c>
+      <c r="B37" s="51">
         <v>0.5223880597014925</v>
       </c>
-      <c r="C37" s="49">
+      <c r="C37" s="51">
         <v>0.5235329064624727</v>
       </c>
-      <c r="D37" s="49">
+      <c r="D37" s="51">
         <v>0.5245214606926754</v>
       </c>
-      <c r="E37" s="49">
+      <c r="E37" s="51">
         <v>0.5259253600213912</v>
       </c>
-      <c r="F37" s="49">
+      <c r="F37" s="51">
         <v>0.5267451190157796</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="B38" s="49">
+        <v>170</v>
+      </c>
+      <c r="B38" s="51">
         <v>0.014925373134328358</v>
       </c>
-      <c r="C38" s="49">
+      <c r="C38" s="51">
         <v>0.01320219156379959</v>
       </c>
-      <c r="D38" s="49">
+      <c r="D38" s="51">
         <v>0.011772184682033292</v>
       </c>
-      <c r="E38" s="49">
+      <c r="E38" s="51">
         <v>0.009549639023644906</v>
       </c>
-      <c r="F38" s="49">
+      <c r="F38" s="51">
         <v>0.008357849692431132</v>
       </c>
     </row>
@@ -4698,26 +5014,26 @@
       <c r="H1" s="18"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="B2" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="52" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
+      <c r="B4" s="54" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="3">
